--- a/results/Int Task Remove ACC -0.4/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.007096575131132332 +/- 0.0016326759093271252</t>
+          <t>0.009009564949089754 +/- 0.0014524655718530933</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0037334156124653297 +/- 0.001290374801994841</t>
+          <t>0.0047207651959271235 +/- 0.0011712590494354917</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0022215365627892393 +/- 0.0015290974012173778</t>
+          <t>0.00435050910212893 +/- 0.0017148649468176833</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0005862388151804731 +/- 0.0019042609224571975</t>
+          <t>6.170934896631009e-05 +/- 0.0016546853042631164</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0010182042579450657 +/- 0.001393934834690101</t>
+          <t>0.009441530391854325 +/- 0.0016454540729371738</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.005430422709040372 +/- 0.0019862359690750965</t>
+          <t>0.011107682813946274 +/- 0.002920619454785362</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.0001234186979327534 +/- 0.00044069289901530725</t>
+          <t>0.0009256402344954839 +/- 0.0004363509911672418</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.004103671706263479 +/- 0.0018463886825519362</t>
+          <t>0.010829990743597629 +/- 0.0019874338679652</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0021906818883060454 +/- 0.002419486568357349</t>
+          <t>0.016167849429188485 +/- 0.0027912824135510085</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.005399568034557189 +/- 0.002560194388017153</t>
+          <t>0.014347423634680622 +/- 0.0024693379789838725</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.001265041653810506 +/- 0.0019192004369125435</t>
+          <t>0.005553841406973126 +/- 0.0018044050005817268</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.004381363776612124 +/- 0.0013853714483581406</t>
+          <t>0.0012958963282936776 +/- 0.0017551944033727884</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.012928108608454147 +/- 0.0021352237305517874</t>
+          <t>0.007158284480098675 +/- 0.001998659023844703</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.009194692995988851 +/- 0.0027243122560498705</t>
+          <t>0.006325208269052718 +/- 0.002848840683835148</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.013390928725701901 +/- 0.002725709697668364</t>
+          <t>0.02252391237272443 +/- 0.001881882219312163</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.005368713360074095 +/- 0.0012123963409064096</t>
+          <t>0.0019129898179573667 +/- 0.0017278617710583207</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.00033940141931496635 +/- 0.0017478567156147577</t>
+          <t>0.003856834310397983 +/- 0.0012590068351189883</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.0036099969145325984 +/- 0.0007811779636637982</t>
+          <t>-0.002962048750385737 +/- 0.0012202233837263364</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.005060166615242168 +/- 0.001506517200337404</t>
+          <t>0.007867941993211947 +/- 0.0015005018717417825</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9.256402344953729e-05 +/- 0.0005172185934662123</t>
+          <t>0.0009873495834618496 +/- 0.0004936747917309248</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.0027769207034866405 +/- 0.0019169669320591334</t>
+          <t>0.009132983647022475 +/- 0.0015001846073610867</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.00857759950632525 +/- 0.001136189610584484</t>
+          <t>-0.0004628201172477975 +/- 0.003561677377542494</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0031471767972847454 +/- 0.001039944433591658</t>
+          <t>0.0024066646096883026 +/- 0.001705680340769539</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0028386300524529174 +/- 0.0011773393414587412</t>
+          <t>6.170934896632119e-05 +/- 0.001136189610584505</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.003733415612465263 +/- 0.002179353703969177</t>
+          <t>-0.006664609688367851 +/- 0.001428674718024097</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-3.0854674483216105e-05 +/- 0.0006239971742103404</t>
+          <t>-0.0008022215365628526 +/- 0.0006353366331988235</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.010614008022215316 +/- 0.0033833385157353534</t>
+          <t>0.028355445850046235 +/- 0.002473960047565693</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.016630669546436327 +/- 0.0023475926641934146</t>
+          <t>-0.01027460660290037 +/- 0.0025520005531320276</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.005121875964208633 +/- 0.0013812421651094844</t>
+          <t>0.0022832459117555605 +/- 0.0018054598998244894</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.009441530391854424 +/- 0.001628004437923235</t>
+          <t>0.00425794507867937 +/- 0.0017980626083719173</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0001851280468991412 +/- 0.0007950693444446374</t>
+          <t>0.00046282011724774197 +/- 0.00028446604311300425</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0006788028386300104 +/- 0.0005982943359970754</t>
+          <t>0.0008947855600123011 +/- 0.00044606085451404825</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0027460660290034465 +/- 0.001551655780398663</t>
+          <t>-0.007343412526997883 +/- 0.001860513845317055</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.0013267510027769713 +/- 0.002164450466805993</t>
+          <t>-0.00950323974082079 +/- 0.0022998636412939304</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.00203640851589012 +/- 0.0010158640933757696</t>
+          <t>0.0024992286331378733 +/- 0.0008098984725952979</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00601666152422089 +/- 0.0014156210733667894</t>
+          <t>-0.00040111076828145407 +/- 0.0006906210825547561</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0037334156124652408 +/- 0.0019487359055400352</t>
+          <t>0.0017895711200246133 +/- 0.001613908896096513</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.007775377969762465 +/- 0.0010490589324282568</t>
+          <t>-0.009595803764270328 +/- 0.0013267510027769216</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.0001851280468991301 +/- 0.0003951326280427823</t>
+          <t>0.00043196544276452586 +/- 0.0009379009042623002</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0038259796359148 +/- 0.0015253572470605625</t>
+          <t>-6.170934896641001e-05 +/- 0.001671856486781113</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.000709657513113271 +/- 0.0019516648689748407</t>
+          <t>-0.0029929034248688978 +/- 0.0022422242886793115</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.009842641160135723 +/- 0.0015017702590111612</t>
+          <t>0.010922554767047166 +/- 0.0013812421651095048</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.0016044430731256276 +/- 0.0014976440727567583</t>
+          <t>0.0006170934896636449 +/- 0.0017399410280619404</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.004319654427645836 +/- 0.002097210178089047</t>
+          <t>0.01098426411601352 +/- 0.0020614986841703286</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0011416229558778523 +/- 0.0015430422400555298</t>
+          <t>0.00027769207034860076 +/- 0.0012903748019948555</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0021906818883060454 +/- 0.001641109058558732</t>
+          <t>-0.0008947855600123678 +/- 0.0015820356363214292</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.00046282011724774197 +/- 0.00031616633032888403</t>
+          <t>0.0007096575131132043 +/- 0.00033940141931501074</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0016044430731256166 +/- 0.001255599503201228</t>
+          <t>-0.00015427337241598061 +/- 0.0018266905418840552</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>-0.0001542733724159584 +/- 0.0020197442578282114</t>
+          <t>-0.002962048750385737 +/- 0.0010969693819581003</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0008022215365627528 +/- 0.00166843638810192</t>
+          <t>-0.00425794507867947 +/- 0.0009639308455299685</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0029929034248688422 +/- 0.0019613964918621133</t>
+          <t>-0.0004628201172478197 +/- 0.0018109880395963225</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.0001542733724158918 +/- 0.0006054124304334709</t>
+          <t>0.001234186979327312 +/- 0.0005689320862260085</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0002159827213822685 +/- 0.0005353085952760643</t>
+          <t>0.0008022215365627528 +/- 0.000664630028649708</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.0031471767972848673 +/- 0.000332315014324854</t>
+          <t>-0.0007713668620796699 +/- 0.00046282011724776045</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-0.005893242826288225 +/- 0.0016236127265563556</t>
+          <t>0.006633755013884568 +/- 0.0019720458107096123</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.0007713668620796477 +/- 0.002488539963150785</t>
+          <t>0.0017587164455414527 +/- 0.0018566721855390602</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.0011416229558778635 +/- 0.0005528069382032967</t>
+          <t>0.000431965442764537 +/- 0.0008528401703847699</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.006942301758716396 +/- 0.0015318965241970263</t>
+          <t>0.006356062943535923 +/- 0.0012885290353484265</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.007189139154581958 +/- 0.0015976048708422816</t>
+          <t>-0.001357605677260143 +/- 0.0017355582981086577</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-3.0854674483227204e-05 +/- 0.001008811028958455</t>
+          <t>0.0012958963282936776 +/- 0.0006442645176741792</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.0020672631903733696 +/- 0.0011129089044659966</t>
+          <t>0.002190681888306034 +/- 0.0008556263266807915</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.004967602591792719 +/- 0.001681225884088268</t>
+          <t>-0.003949398333847609 +/- 0.0022707028069082614</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.011663066954643652 +/- 0.0025248099408180973</t>
+          <t>0.011663066954643597 +/- 0.002068874373864888</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.002406664609688336 +/- 0.0012631588701301174</t>
+          <t>0.004998457266275791 +/- 0.0010847513626193927</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.0003394014193150108 +/- 0.00025629817534457563</t>
+          <t>0.0004936747917309248 +/- 0.0002827877627248153</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.004936747917309437 +/- 0.0015115641732694658</t>
+          <t>0.0008947855600123011 +/- 0.0016925131936936164</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0011107682813945806 +/- 0.001481024375192839</t>
+          <t>0.0021598272138228292 +/- 0.0009854192793996492</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0011107682813945806 +/- 0.0003146571745506049</t>
+          <t>6.170934896633229e-05 +/- 0.0005982943359970891</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.005214439987658093 +/- 0.0010088110289584455</t>
+          <t>0.013174946004319621 +/- 0.0014541032604687713</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0005862388151805398 +/- 0.0011163253634758313</t>
+          <t>0.004134526380746628 +/- 0.0009969450429746212</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.004165381055229833 +/- 0.0017467670292771477</t>
+          <t>0.0005245294662140742 +/- 0.0008399048188100081</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00023899928085203582</t>
+          <t>6.17093489663545e-05 +/- 0.000185128046899119</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.0015118790496760793 +/- 0.0009199661534017741</t>
+          <t>6.170934896634339e-05 +/- 0.00033231501432488906</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.0009873495834618385 +/- 0.000765792881579188</t>
+          <t>-0.0004936747917309803 +/- 0.0010344371869324405</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.00027769207034870067 +/- 0.000709657513113255</t>
+          <t>-0.0002468373958655401 +/- 0.0005308438918261588</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.005584696081456319 +/- 0.001758716445541505</t>
+          <t>0.00018512804689905238 +/- 0.0011805693594389907</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>6.17093489663656e-05 +/- 0.0003598242452850993</t>
+          <t>0.000308546744831828 +/- 0.000308546744831828</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0001851280468991301 +/- 0.0014219955102502974</t>
+          <t>0.002499228633137851 +/- 0.0014236682499301895</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.002406664609688314 +/- 0.0019258854099755897</t>
+          <t>0.002530083307621056 +/- 0.0008256148201332779</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0014501697007097026 +/- 0.0008169208451017466</t>
+          <t>-0.0017278617710583476 +/- 0.00037025609379819356</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.002530083307621056 +/- 0.0011021642147171697</t>
+          <t>-0.002375809935205231 +/- 0.0013021257541505095</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.001079913606911398 +/- 0.0012740402852244818</t>
+          <t>-0.0007713668620796699 +/- 0.0012514223875762535</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.00037025609379823796 +/- 0.0007008834737180351</t>
+          <t>0.0008639308855291183 +/- 0.001471997586161872</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.000892060660124916 +/- 0.0004410465945343829</t>
+          <t>0.0005649717514124353 +/- 0.0010592633440711671</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.0006244424620874267 +/- 0.002219022682938523</t>
+          <t>0.0003865596193874499 +/- 0.0016451473319801437</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.002259887005649741 +/- 0.0011909000531965953</t>
+          <t>0.0018435920309248011 +/- 0.001274117471640107</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0024680344930121723 +/- 0.0013499327342035266</t>
+          <t>-0.0016651798988997712 +/- 0.0009969107709925842</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.001575973832887312 +/- 0.0015960436396455044</t>
+          <t>0.0025572405590246873 +/- 0.0012056577420584843</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0031222123104371 +/- 0.0018864968094632068</t>
+          <t>0.0021706809396372486 +/- 0.001498909683155352</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00041629497472496225 +/- 0.0002725290333009447</t>
+          <t>0.0005649717514124575 +/- 0.000555502280471865</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.002943800178412126 +/- 0.0011474148903701964</t>
+          <t>0.0009812667261373976 +/- 0.0011209085236378738</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.008147487362473994 +/- 0.002342119377640829</t>
+          <t>0.001873327386262269 +/- 0.0027577037299105736</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.007285162057686589 +/- 0.0027806929743100744</t>
+          <t>-0.0021409455842997136 +/- 0.001984932413711428</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.003954802259887047 +/- 0.0011443283618729687</t>
+          <t>-0.00014867677668747303 +/- 0.0007192022969044328</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0011002081474873581 +/- 0.0011129924039377246</t>
+          <t>0.0037763901278620284 +/- 0.0013822942966600724</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.0028545941123996775 +/- 0.0011377416871667487</t>
+          <t>0.0039548022598870245 +/- 0.0011520291779845535</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.005947071067499254 +/- 0.0021110008146653265</t>
+          <t>0.003925066904549512 +/- 0.002511889632107383</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.01022896223609875 +/- 0.002090799385221163</t>
+          <t>-0.00927743086529883 +/- 0.001865523299596567</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.0005055010407374217 +/- 0.0013433668745853698</t>
+          <t>0.0009812667261373865 +/- 0.0015510914487951277</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.000535236396074934 +/- 0.0011953464907666887</t>
+          <t>-0.002022004162949731 +/- 0.0012317761033129974</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0007433838834374207 +/- 0.0011535631722433143</t>
+          <t>-0.0011894142134998176 +/- 0.0014567289579441986</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0019625334522747617 +/- 0.0007776804537985235</t>
+          <t>0.0010110020814748989 +/- 0.0016188709591217567</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>8.92060660124705e-05 +/- 0.00013626451665045783</t>
+          <t>0.00038655961938747205 +/- 0.00037729936189261857</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.011121022896223609 +/- 0.0020437514454284375</t>
+          <t>-0.0050252750520368705 +/- 0.0030132641844878663</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.004876598275349387 +/- 0.001212969256876083</t>
+          <t>-0.00038655961938743877 +/- 0.0013167760823957675</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.001903062741599748 +/- 0.0008325899494498809</t>
+          <t>-0.0008920606601248604 +/- 0.0011125951194689235</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0011596788581623384 +/- 0.0011161655890052676</t>
+          <t>-0.00014867677668747303 +/- 0.0008540830577665954</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.000802854594112401 +/- 0.0007528390663795614</t>
+          <t>0.0005352363960749451 +/- 0.0009662846749492736</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0001784121320249965 +/- 0.0005515086824558791</t>
+          <t>-0.000178412132024941 +/- 0.0006122884413313742</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.007939339875111528 +/- 0.0018667078341622974</t>
+          <t>-0.0018733273862622467 +/- 0.0018524434287448789</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.00636336604222425 +/- 0.0016297579073499596</t>
+          <t>-0.0036871840618495242 +/- 0.0012056577420584706</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.0020814748736247223 +/- 0.001474825663709452</t>
+          <t>-0.0016651798988997935 +/- 0.000988001648875175</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0009812667261373976 +/- 0.0011748287995919308</t>
+          <t>-0.0011596788581623497 +/- 0.0016256838457135415</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.0003568242640499708 +/- 0.000576589932490801</t>
+          <t>0.0007433838834374096 +/- 0.0003819575551193819</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0007731192387749108 +/- 0.0007307883275316286</t>
+          <t>0.00023788284269998794 +/- 0.0005450580666019294</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.006690454950936664 +/- 0.000970393629026505</t>
+          <t>-0.0005649717514124353 +/- 0.0011082155904599705</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.0010110020814748765 +/- 0.0010981971639975766</t>
+          <t>-0.002735652691049628 +/- 0.0008494116477600557</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0025572405590247095 +/- 0.0007545987237852889</t>
+          <t>-0.002170680939637215 +/- 0.0006244424620874166</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00020814748736245337 +/- 0.0004000482916168351</t>
+          <t>-0.00011894142134996066 +/- 0.00035682426404996527</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.0024085637823372252 +/- 0.0020274628526590404</t>
+          <t>0.003984537615224526 +/- 0.001357444211776778</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0011299435028248594 +/- 0.0010110020814748525</t>
+          <t>0.0014272970561998277 +/- 0.0008389376140152158</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.00032708890871248065 +/- 0.0005711975234106013</t>
+          <t>0.0011002081474873692 +/- 0.0007759731400951456</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>8.92060660124927e-05 +/- 0.0008725186292667941</t>
+          <t>-0.0033006244424620633 +/- 0.001116165589005265</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.001873327386262258 +/- 0.001039036884309033</t>
+          <t>0.0033006244424620967 +/- 0.001243563703022667</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0033600951531370994 +/- 0.0010969888043827866</t>
+          <t>-0.0041332143919119765 +/- 0.001878041352915624</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.01308355634849837 +/- 0.0017989275601848526</t>
+          <t>-0.008890871245911392 +/- 0.0014411681018201264</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.0040142729705619825 +/- 0.0010823832722688831</t>
+          <t>0.007344632768361592 +/- 0.0022214121552922754</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0015462384775497772 +/- 0.0010868668975615176</t>
+          <t>0.003211418376449615 +/- 0.001217335087151855</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.0030032708890870953 +/- 0.0017208012246482573</t>
+          <t>0.002378828426999735 +/- 0.0009862101666236705</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.00011894142134996066 +/- 0.0005515086824558791</t>
+          <t>-0.00020814748736245337 +/- 0.00023224054938763875</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.000981266726137353 +/- 0.0015453804888713972</t>
+          <t>0.0007731192387749108 +/- 0.001618870959121778</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0034195658638120573 +/- 0.0012205992121185727</t>
+          <t>-0.0038655961938744987 +/- 0.001021442999543136</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.0032708890871246286 +/- 0.0011516453601568186</t>
+          <t>-0.005144216473386853 +/- 0.0013629695672156903</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.012667261373773409 +/- 0.0023345568155088326</t>
+          <t>-0.010674992566161178 +/- 0.002301178401896615</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0002676181980374892 +/- 0.0006839131727624027</t>
+          <t>5.947071067501364e-05 +/- 0.00047576568539994953</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0005352363960749562 +/- 0.00034677085309813417</t>
+          <t>0.0001784121320250076 +/- 0.0005976732453833479</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.00011894142134996066 +/- 0.0001456728957943904</t>
+          <t>0.0003568242640499708 +/- 0.00029134579158884193</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.00877192982456142 +/- 0.0016886435759144636</t>
+          <t>-0.0001784121320249854 +/- 0.0012488849241748398</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.008920606601248892 +/- 0.0014445385431449442</t>
+          <t>-0.0038358608385370085 +/- 0.0016147694299595997</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.0009217960154623949 +/- 0.0007092988665998776</t>
+          <t>-0.00023788284269996574 +/- 0.0004757656853999523</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.0011299435028248594 +/- 0.0007956638810740069</t>
+          <t>0.003092476955099621 +/- 0.0012202369627524968</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.007314897413024102 +/- 0.0012056577420584806</t>
+          <t>-0.005352363960749307 +/- 0.0013496051998703735</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0011002081474873581 +/- 0.0006655673293368755</t>
+          <t>-0.0009217960154623728 +/- 0.0005226998463053126</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.004876598275349364 +/- 0.0010144943270432329</t>
+          <t>0.0010704727921499013 +/- 0.0011454867846719147</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.00802854594112401 +/- 0.001426057544844701</t>
+          <t>-0.004281891168599439 +/- 0.0010487774063960007</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.0022004162949747054 +/- 0.0020263722910973396</t>
+          <t>0.0011002081474873581 +/- 0.001533894781627001</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.004400832589949421 +/- 0.0013613467906345054</t>
+          <t>0.002497769848349707 +/- 0.0007662265076851196</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.00032708890871242514 +/- 0.000247000412218807</t>
+          <t>8.92060660125038e-05 +/- 0.00013626451665050873</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.006303895331549203 +/- 0.0012531256322156096</t>
+          <t>0.0052631578947368585 +/- 0.0008925561117932731</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.002824858757062132 +/- 0.0016675676351840466</t>
+          <t>0.003597977995837065 +/- 0.0013127410083047192</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.0009812667261373642 +/- 0.0006655673293369098</t>
+          <t>-8.92060660124705e-05 +/- 0.00046161685091465827</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.0048765982753493755 +/- 0.0015576331672564818</t>
+          <t>0.007969075230449008 +/- 0.0015266723345814274</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.002557240559024654 +/- 0.0008000965832336271</t>
+          <t>0.0010110020814748655 +/- 0.0014518650747230152</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.0027059173357121603 +/- 0.0011927547499334683</t>
+          <t>0.0038061254831995295 +/- 0.0012245768826627437</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-0.00014867677668751745 +/- 0.0001994708276092673</t>
+          <t>-0.00014867677668746194 +/- 0.0002741464304874461</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.0004757656853999315 +/- 0.0008000965832336609</t>
+          <t>-0.00011894142134997177 +/- 0.0004247058238800259</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.00032708890871242514 +/- 0.00048769608881526555</t>
+          <t>-0.0003568242640499264 +/- 0.000725932537361511</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.00020814748736245337 +/- 0.0005649717514124394</t>
+          <t>-0.00029735355337495717 +/- 0.00044104659453440533</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.003062741599762109 +/- 0.0014201550920320575</t>
+          <t>0.0025869759143621997 +/- 0.0011971942990899479</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.00020814748736245337 +/- 0.00040004829161684327</t>
+          <t>0.00020814748736250888 +/- 0.00023224054938764585</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0009217960154623839 +/- 0.001422643320119618</t>
+          <t>0.00041629497472496225 +/- 0.0007776804537984963</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.0057091882247992665 +/- 0.0016057091882248045</t>
+          <t>0.0022004162949747497 +/- 0.0015405095268496763</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.0005352363960749229 +/- 0.0007011493382427409</t>
+          <t>-0.000178412132024941 +/- 0.0005352363960749279</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0015759738328872896 +/- 0.001655861527484484</t>
+          <t>0.0038358608385370306 +/- 0.0010675779405897204</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.0010407374368123668 +/- 0.0008745430371604436</t>
+          <t>0.0016651798988998156 +/- 0.0008940408194096339</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.00023788284269998794 +/- 0.00039448406664945523</t>
+          <t>-0.0008028545941123899 +/- 0.0007759731400951578</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.005316606929510126 +/- 0.0018010529786955114</t>
+          <t>-0.0020011947431301967 +/- 0.0016253008196430933</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00719832735961764 +/- 0.0014414490456408128</t>
+          <t>0.010155316606929542 +/- 0.0014814333055719411</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0001792114695340019 +/- 0.0017168587650179088</t>
+          <t>-0.0006869772998805091 +/- 0.000944999523270987</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.000477897252090842 +/- 0.0017168587650179007</t>
+          <t>0.005585424133811257 +/- 0.0012885098333406929</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0002389486260454543 +/- 0.0011397123075471264</t>
+          <t>0.0064516129032258455 +/- 0.0014399009310864849</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0011051373954599208 +/- 0.0020215975219853985</t>
+          <t>-0.0013739545997610292 +/- 0.001581625124835568</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00020908004778965594 +/- 0.00032855436081239727</t>
+          <t>-8.960573476702871e-05 +/- 0.0001368750207573484</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.006332138590203073 +/- 0.0013477316813235993</t>
+          <t>0.0012843488649940781 +/- 0.0005981178134558422</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.015949820788530432 +/- 0.0020398292806408274</t>
+          <t>0.021594982078853086 +/- 0.0026177214593316057</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.016099163679808803 +/- 0.002212896827000172</t>
+          <t>0.026523297491039467 +/- 0.0033468804845475427</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.014456391875746755 +/- 0.0011736489070721878</t>
+          <t>-0.002090800477897237 +/- 0.0014993907285556652</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.0020011947431302747 +/- 0.0018170801880830563</t>
+          <t>-0.0030167264038231446 +/- 0.001459898376326174</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.010692951015531627 +/- 0.002730321357712404</t>
+          <t>0.010454002389486284 +/- 0.0012459171812792317</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.0052867383512545385 +/- 0.003075303396793556</t>
+          <t>0.0026881720430107837 +/- 0.003046009267379208</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.017980884109916308 +/- 0.0019667954161474628</t>
+          <t>0.028703703703703752 +/- 0.0017943534403674578</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.004032258064516192 +/- 0.0019913629988988456</t>
+          <t>-0.003614097968936647 +/- 0.0011211663308914848</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.006421744324970102 +/- 0.0019597520552358666</t>
+          <t>0.0033154121863799733 +/- 0.001284348864994021</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0028076463560334 +/- 0.001433691756272413</t>
+          <t>-0.005346475507765802 +/- 0.0008174391985307052</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.004689366786140947 +/- 0.0015056252283307686</t>
+          <t>0.0006571087216248773 +/- 0.0011857487001958992</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.00044302260974284416</t>
+          <t>0.00011947431302270495 +/- 0.00019812573419089211</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0013440860215054196 +/- 0.0021507450450889837</t>
+          <t>-0.008154121863799269 +/- 0.0022631238637412818</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>8.96057347669843e-05 +/- 0.0014389712628967706</t>
+          <t>-0.0025388291517323357 +/- 0.0009374166563007867</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.004928315412186324 +/- 0.0011353989133063484</t>
+          <t>0.004898446833930726 +/- 0.0008779533128255036</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.00026881720430113056 +/- 0.0010555912214499576</t>
+          <t>0.004719235364396701 +/- 0.0014060456745447942</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0010454002389486683 +/- 0.0007099680002392589</t>
+          <t>0.008124253285543637 +/- 0.0009797622142686218</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.00014934289127842558 +/- 0.0006972889802824676</t>
+          <t>-0.0006869772998805091 +/- 0.0002688172043010392</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.007019115890083583 +/- 0.0022639121340068333</t>
+          <t>0.011439665471923577 +/- 0.0034576669142606835</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.015412186379928361 +/- 0.0016316009896950483</t>
+          <t>0.002479091995221061 +/- 0.0017316049033017623</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.014307048984468395 +/- 0.0022647001299005327</t>
+          <t>-0.003912783751493398 +/- 0.0016438575753664165</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0016726403823178581 +/- 0.0012184037069516774</t>
+          <t>0.01603942652329753 +/- 0.0021828597838223873</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.00029868578255671797 +/- 0.0007068195678732931</t>
+          <t>-0.000418160095579434 +/- 0.0004051571077135535</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.0014635603345281357 +/- 0.0005077658303464961</t>
+          <t>-0.0011350059737156193 +/- 0.0004778972520907823</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.0018219832735961172 +/- 0.0016438575753664174</t>
+          <t>0.009438470728793325 +/- 0.0021463852118544465</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.012216248506571136 +/- 0.0016492757099496446</t>
+          <t>-0.006481481481481444 +/- 0.0011494552810569836</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0006869772998805534 +/- 0.0004234601815638709</t>
+          <t>0.00014934289127838118 +/- 0.0004276529588792393</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.00047789725209083087 +/- 0.0005033542277883161</t>
+          <t>-0.0005675029868578152 +/- 0.0006329038261773146</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.00029868578255668463 +/- 0.0010851793383861988</t>
+          <t>0.005704898446833961 +/- 0.0017693193810776428</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.0016427718040621596 +/- 0.0009655453927864162</t>
+          <t>-0.005675029868578219 +/- 0.0018412228204805843</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0018219832735962282 +/- 0.0009581251453014015</t>
+          <t>-0.0022102747909199306 +/- 0.0006003509928985243</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0009539258914379452</t>
+          <t>0.0034348864994026675 +/- 0.0009655453927864401</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0026583034647551184 +/- 0.0011369693136603519</t>
+          <t>-0.00044802867383509916 +/- 0.0014088980185269606</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-5.973715651139688e-05 +/- 0.0015451036029124887</t>
+          <t>0.0013739545997610847 +/- 0.0009079261740484349</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.013142174432496956 +/- 0.0018890547551782388</t>
+          <t>0.004480286738351313 +/- 0.0018508880985459593</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.02795698924731178 +/- 0.0024051161456627836</t>
+          <t>0.02123655913978496 +/- 0.0017893746476404042</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.004838709677419317 +/- 0.0008738792615488659</t>
+          <t>0.0011947431302270495 +/- 0.0008125131725648742</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0016726403823177582 +/- 0.0013894508183528217</t>
+          <t>-0.001105137395459943 +/- 0.000991078854422763</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.00038829151732381326 +/- 0.0008347185551064583</t>
+          <t>-0.0002389486260453988 +/- 0.00032169443292319846</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0028673835125447634 +/- 0.0007218068084584422</t>
+          <t>0.00026881720430113056 +/- 0.0014038231780167131</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.004360812425328519 +/- 0.0018662484291294044</t>
+          <t>0.004808841099163685 +/- 0.0018190430081941648</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.012753882915173275 +/- 0.0010773410272922042</t>
+          <t>0.0020310633213859288 +/- 0.0015566086285299283</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.004749103942652377 +/- 0.0025005905216190115</t>
+          <t>0.014486260454002397 +/- 0.002524734224492739</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.0014635603345280247 +/- 0.0007370945447582774</t>
+          <t>-0.0002389486260453766 +/- 0.0005138784508388448</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0002986857825567846 +/- 0.00048161635294494023</t>
+          <t>-0.00026881720430107505 +/- 0.0003118371119746184</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.0036140979689367136 +/- 0.00047131821499582255</t>
+          <t>-0.0003285543608124164 +/- 0.00047131821499579583</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0005675029868577597 +/- 0.0016220040600221628</t>
+          <t>0.012903225806451635 +/- 0.0020027544341983676</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.006690561529271166 +/- 0.0015872557055658682</t>
+          <t>-0.0052867383512544604 +/- 0.0014012788656797984</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.0007467144563919059 +/- 0.0005216322938044709</t>
+          <t>2.9868578255676238e-05 +/- 0.00031183711197464074</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-2.9868578255709544e-05 +/- 0.001794353440367461</t>
+          <t>0.005585424133811278 +/- 0.0016362420459739946</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.005824372759856667 +/- 0.0012619253389652028</t>
+          <t>0.00988649940262849 +/- 0.0020409223782385235</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.000597371565113447 +/- 0.000566716426553455</t>
+          <t>-5.9737156511352477e-05 +/- 0.00032169443292322117</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.0033154121863799733 +/- 0.001946963977028946</t>
+          <t>0.0013440860215053973 +/- 0.0010538995677644837</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.011111111111111172 +/- 0.001661938798475932</t>
+          <t>0.00809438470728795 +/- 0.0022764873371913185</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.00044802867383507693 +/- 0.001275986222418991</t>
+          <t>0.014127837514934304 +/- 0.0016253008196430894</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.003763440860215006 +/- 0.0016694371102129071</t>
+          <t>0.005675029868578274 +/- 0.0012672164537393313</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>8.96057347669732e-05 +/- 0.0004018406226724234</t>
+          <t>0.0006869772998805534 +/- 0.0003789897712201324</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0004778972520907643 +/- 0.0020134169111532623</t>
+          <t>0.0009856630824372937 +/- 0.0013755769342496571</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.008781362007168492 +/- 0.001856663114446861</t>
+          <t>0.003405017921147002 +/- 0.0014886422693401772</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.001373954599761118 +/- 0.0007461168456867912</t>
+          <t>-0.0007765830346475155 +/- 0.0005376344086021267</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.02640382317801667 +/- 0.0036732279903568</t>
+          <t>0.023297491039426566 +/- 0.0024954120160340884</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.0026881720430107945 +/- 0.0007437216008356326</t>
+          <t>-0.0007168458781361853 +/- 0.0009557945041815896</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.002718040621266382 +/- 0.001754127462368704</t>
+          <t>-0.0028375149342890872 +/- 0.001135398913306341</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-5.9737156511374676e-05 +/- 0.00026038822840742764</t>
+          <t>0.0002389486260454099 +/- 0.00032169443292322117</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.001762246117084787 +/- 0.0011051373954599816</t>
+          <t>-0.0005973715651134915 +/- 0.0006265285831362742</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.0008960573476701983 +/- 0.0008553059177584438</t>
+          <t>0.00035842293906813706 +/- 0.0010669397311524422</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,52 +2156,52 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-2.9868578255720647e-05 +/- 0.0008905646066831184</t>
+          <t>-5.973715651133027e-05 +/- 0.0007879872137558535</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.00044802867383508804 +/- 0.0013638530533848195</t>
+          <t>0.002658303464755074 +/- 0.00024810704489003615</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.9737156511352477e-05 +/- 0.00011947431302270495</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.0019713261648746094 +/- 0.0005539795994919652</t>
+          <t>0.0010454002389486572 +/- 0.0008985429484164594</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0007168458781361631 +/- 0.0008677323205695255</t>
+          <t>0.002090800477897281 +/- 0.001940308455067107</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0018219832735962061 +/- 0.0013781686971396914</t>
+          <t>0.008393070489844723 +/- 0.0011211663308914675</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.0018817204301075808 +/- 0.0008347185551064592</t>
+          <t>-0.0022102747909199306 +/- 0.0010364009302806139</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.0027777777777778347 +/- 0.0011800923694825797</t>
+          <t>-0.00567502986857823 +/- 0.0013490549331704087</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.004002389486260405 +/- 0.0012401755968952607</t>
+          <t>0.009348864994026328 +/- 0.0020391731408241544</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.003166069295101592 +/- 0.001019039552522823</t>
+          <t>-0.0003285543608123942 +/- 0.0009946729871772246</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0026678932842686075 +/- 0.0016686621110595307</t>
+          <t>-0.0040785035265255565 +/- 0.0013853857096689903</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.0010732904017172196 +/- 0.0021212417792727508</t>
+          <t>0.004231830726770969 +/- 0.0017975284746706876</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.00849432689359092 +/- 0.0009506286415210262</t>
+          <t>0.0014412756823060757 +/- 0.001490037487059948</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.00279055504446486 +/- 0.0015783022670908206</t>
+          <t>-0.015976694265562662 +/- 0.002416351060176856</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0007666360012266394 +/- 0.0023162051641560043</t>
+          <t>0.0013186139221098125 +/- 0.0018247869422645482</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0004906470407850638 +/- 0.0019111237596912364</t>
+          <t>0.001349279362158917 +/- 0.0013864035026626485</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.0011652867218644336 +/- 0.0003830112234528155</t>
+          <t>-0.0001533272002452679 +/- 0.0004991971970591674</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00708371665133396 +/- 0.0019799998107768047</t>
+          <t>-0.0035571910456914657 +/- 0.002098735189484056</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.011376878258203016 +/- 0.002706387962431541</t>
+          <t>0.028580190125728357 +/- 0.004400891309637593</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.030972094449555378 +/- 0.0043302381129969765</t>
+          <t>0.03342532965348057 +/- 0.0034202621266111338</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0019319227230910952 +/- 0.001900515232425151</t>
+          <t>0.000275988960441631 +/- 0.0018009257111347584</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>6.133088009815379e-05 +/- 0.0018027523405947888</t>
+          <t>0.0019625881631401888 +/- 0.0007660224469056648</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.0026985587243176677 +/- 0.0024099212148897195</t>
+          <t>0.0012266176019626318 +/- 0.0016284474759094448</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.009352959214964717 +/- 0.002551873194893158</t>
+          <t>0.002851885924563069 +/- 0.0029414855315841822</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.00886231217417972 +/- 0.002217473926990608</t>
+          <t>-0.0007666360012265838 +/- 0.0033487166004050185</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.00045998160073593695 +/- 0.0012131272888593913</t>
+          <t>0.005458448328733568 +/- 0.0014172609639118274</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.008678319533885315 +/- 0.0012115759745561542</t>
+          <t>-0.002085249923336363 +/- 0.0012403402892460238</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0031892057651026874 +/- 0.0015588181572693933</t>
+          <t>-0.011070223857712303 +/- 0.0010837532687563622</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0012266176019626097 +/- 0.0014119428927594426</t>
+          <t>-0.0007973014412756329 +/- 0.0011813161781207122</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00030665440049066907 +/- 0.0004750669544565936</t>
+          <t>0.0005519779208832176 +/- 0.0003004587234324834</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.008279668813247498 +/- 0.0027496487913474424</t>
+          <t>0.0036491873658387242 +/- 0.002072811360456463</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.005703771849126049 +/- 0.0018612684336698682</t>
+          <t>-0.007175712971481107 +/- 0.0010551763590361976</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.00018399264029440588 +/- 0.0014265198834238365</t>
+          <t>-0.0030665440049064243 +/- 0.0011955589506052</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0022385771235816977 +/- 0.0007391579756635244</t>
+          <t>-0.0016559337626494309 +/- 0.001055176359036188</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.005581110088929775 +/- 0.0009965088506146702</t>
+          <t>-0.0015026065624041407 +/- 0.0014607182292320677</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0004906470407850083 +/- 0.0007782016277491349</t>
+          <t>-0.0006133088009812604 +/- 0.0005977794753026028</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.007329040171726475 +/- 0.0011346212818153841</t>
+          <t>-0.003495860165593334 +/- 0.001509786399888537</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.005213124808340974 +/- 0.0016852047425984808</t>
+          <t>-0.005427782888684407 +/- 0.0014516774460036318</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.005366452008586297 +/- 0.0012587780283210047</t>
+          <t>-0.006807727690892329 +/- 0.0009965088506146476</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.006961054891137686 +/- 0.0014581408681961264</t>
+          <t>-0.013400797301441225 +/- 0.0014516774460036346</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.00030665440049066907 +/- 0.0005311410020143812</t>
+          <t>-0.0014719411223550582 +/- 0.0003576174115207132</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0002453235203924931 +/- 0.0004710914288787914</t>
+          <t>0.00015332720024535673 +/- 0.00015332720024535673</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.006562404170499858 +/- 0.0014265198834238543</t>
+          <t>-0.013462128181539367 +/- 0.0015298950853439258</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.006378411530205452 +/- 0.0022526056635641823</t>
+          <t>-0.004998466727997519 +/- 0.0011395832061368832</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.0007666360012266061 +/- 0.0009721476531215697</t>
+          <t>-0.001134621281815329 +/- 0.000582643360932248</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0002453235203924931 +/- 0.000545120786097255</t>
+          <t>-0.0003373198405396627 +/- 0.0007314848477078549</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.005550444648880726 +/- 0.0015603255729173312</t>
+          <t>-0.0014719411223550693 +/- 0.0017007573902314537</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.007727690892364314 +/- 0.0013904672246249216</t>
+          <t>-0.0006439742410302984 +/- 0.0007931626590847973</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0006746396810794475 +/- 0.0006254547088123738</t>
+          <t>-0.0007053051211284411 +/- 0.0005985655104551838</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.002146580803434506 +/- 0.0010077691950416958</t>
+          <t>0.0010119595216191769 +/- 0.0011313012416864106</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0028518859245629915 +/- 0.0012721538492911158</t>
+          <t>-0.009230297454768421 +/- 0.0013328006017847953</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.001165286721864478 +/- 0.0013972138301005285</t>
+          <t>-0.0005826433609321891 +/- 0.001167302441623671</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.015639374425023 +/- 0.0012643684837833997</t>
+          <t>-0.013676786261882812 +/- 0.0018460493030717303</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.0007973014412756996 +/- 0.0022333200191393156</t>
+          <t>0.003526525605642483 +/- 0.0013171868503474154</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.001379944802207933 +/- 0.0007788055871941438</t>
+          <t>-0.0019012572830419683 +/- 0.001342291850857985</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0014106102422570045 +/- 0.001204960607444862</t>
+          <t>-0.005887764489420378 +/- 0.0021675065375127175</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6.133088009814269e-05 +/- 0.0006548346060736633</t>
+          <t>-0.0006133088009812382 +/- 0.0005818358160383375</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.006071757129714838 +/- 0.001397213830100533</t>
+          <t>-0.006255749770009145 +/- 0.0005687591840230266</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.011499540018399267 +/- 0.0024155725965419174</t>
+          <t>-0.011622201778595487 +/- 0.0016019574224604592</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.011622201778595498 +/- 0.0017851922205247381</t>
+          <t>-0.00947562097516096 +/- 0.003052559341865142</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.020453848512726146 +/- 0.0018705918429929409</t>
+          <t>-0.02388837779822135 +/- 0.0017799168182682044</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>9.199632014720294e-05 +/- 0.0005662736986390592</t>
+          <t>9.199632014723624e-05 +/- 0.0004347576473093353</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6.1330880098176e-05 +/- 0.0005275881795180946</t>
+          <t>0.00015332720024536784 +/- 0.0004799900595675874</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>3.066544004910465e-05 +/- 0.00032015659334285883</t>
+          <t>6.13308800981649e-05 +/- 0.0003302768970950277</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.013799448022079108 +/- 0.002476127474785198</t>
+          <t>-0.016498006746396766 +/- 0.00230215570427764</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.011714198098742723 +/- 0.0020331903654401337</t>
+          <t>-0.01950321987120508 +/- 0.0015946028825513602</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.0012879484820607413 +/- 0.0011292212597069583</t>
+          <t>0.0009199632014719849 +/- 0.0004750669544565793</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.00024532352039248196 +/- 0.0016728833728286779</t>
+          <t>-0.009414290095062805 +/- 0.0017240960192420086</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.020668506593069614 +/- 0.002258442519413924</t>
+          <t>-0.014351425942962215 +/- 0.000996508850614636</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0005519779208831843 +/- 0.0004710914288787668</t>
+          <t>-0.0002146580803433995 +/- 0.0005320255005488167</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.004783808647654075 +/- 0.0011325473972781058</t>
+          <t>-0.00018399264029435037 +/- 0.0016468226411649961</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.018429929469487884 +/- 0.0017956965313655105</t>
+          <t>-0.025329653480527414 +/- 0.0015467059445469005</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.0044158233670653305 +/- 0.0011408203151020155</t>
+          <t>-0.00015332720024527902 +/- 0.001019366460508731</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.013032812020852514 +/- 0.0016810144217927936</t>
+          <t>0.0074210364918737 +/- 0.0007973014412756893</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-3.066544004903804e-05 +/- 0.0002146580803434566</t>
+          <t>0.0007666360012266616 +/- 0.000417095078464753</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.012818153940509048 +/- 0.0012096340339353363</t>
+          <t>0.0022692425636308355 +/- 0.0010189051043137747</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0035878564857405814 +/- 0.0010889470042664605</t>
+          <t>0.00070530512112853 +/- 0.0010175197806217041</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.199632014720294e-05 +/- 0.0005826433609322346</t>
+          <t>-9.199632014714743e-05 +/- 0.0008347536086363657</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.01732597362772157 +/- 0.0020120361487058216</t>
+          <t>0.015332720024532408 +/- 0.001819367920783978</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.004446488807114424 +/- 0.0004170950784647693</t>
+          <t>0.004477154247163495 +/- 0.0014591079120969564</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.012327506899724039 +/- 0.001550349544282669</t>
+          <t>0.00926096289481757 +/- 0.0006829517771027283</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-9.199632014716963e-05 +/- 0.00027598896044159525</t>
+          <t>0.00024532352039255965 +/- 0.0003830112234528404</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0035878564857405814 +/- 0.001164075614603008</t>
+          <t>0.0008586323213738423 +/- 0.0009076141421005228</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0005826433609322113 +/- 0.0005728776967883877</t>
+          <t>0.003802514566084081 +/- 0.000847609626561497</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.0018705918429929747 +/- 0.0007931626590848085</t>
+          <t>0.00030665440049069124 +/- 0.0005485600680772386</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.005458448328733534 +/- 0.0012327354334401353</t>
+          <t>0.00070530512112853 +/- 0.0011395832061369042</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0004906470407850638 +/- 0.0005850593078300974</t>
+          <t>0.0006746396810794697 +/- 0.0005785943656581911</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.00012266176019626318 +/- 0.000880263728574495</t>
+          <t>-0.00024532352039248196 +/- 0.0012096340339353656</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.008279668813247487 +/- 0.001464254693200029</t>
+          <t>0.008157007053051257 +/- 0.0010815818514902592</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.00622508432996014 +/- 0.0007884060185331058</t>
+          <t>0.0020545844832873692 +/- 0.0008786598455623676</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0002453235203924931 +/- 0.0014039280149965726</t>
+          <t>0.007329040171726508 +/- 0.0016425344055003956</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.005918429929469493 +/- 0.0023235015933167165</t>
+          <t>0.005305121128488221 +/- 0.0010715366580592526</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.00015332720024534562 +/- 0.0014334248258227793</t>
+          <t>-0.0001533272002452901 +/- 0.0010007463276344906</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0024667931688804766 +/- 0.0016051331486969828</t>
+          <t>-0.0020240354206198406 +/- 0.0016323197850175747</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0063567362428842865 +/- 0.0016460485363280414</t>
+          <t>0.0015180265654649028 +/- 0.0015350614926643539</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0013915243516761544 +/- 0.001012017710309948</t>
+          <t>-0.00025300442757747454 +/- 0.0015609060947821577</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.00164452877925364 +/- 0.0010277088430912077</t>
+          <t>0.002751423149905119 +/- 0.002107553077994456</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.006578115117014583 +/- 0.0018045974215923004</t>
+          <t>-0.017678684376976606 +/- 0.001203849861522709</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.000980392156862775 +/- 0.0017347992602027092</t>
+          <t>0.0013598987982289755 +/- 0.0014904328485702946</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0005376344086021279 +/- 0.00028462998102468786</t>
+          <t>0.0004743833017077925 +/- 0.0006364519860056277</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.015654648956356765 +/- 0.0013135078847119153</t>
+          <t>-0.011005692599620476 +/- 0.00099808563175584</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0012017710309930262 +/- 0.0015736692352466448</t>
+          <t>0.008032890575585072 +/- 0.0032474377363677378</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.011132194813409203 +/- 0.002810228955284389</t>
+          <t>0.01695129664769134 +/- 0.0026277771129463575</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.005913978494623673 +/- 0.0014769505918830535</t>
+          <t>-0.0022454142947501256 +/- 0.0011955128508182057</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.0026565464895635825 +/- 0.0014437333599637218</t>
+          <t>0.0007906388361796246 +/- 0.0015828581601824458</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.0037634408602150947 +/- 0.0019051607187639658</t>
+          <t>-0.004269449715369999 +/- 0.0009824303963952641</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0012650221378873727 +/- 0.0028985298513319654</t>
+          <t>0.0032258064516129 +/- 0.0034085246262637366</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0011701454775458475 +/- 0.001470163099199162</t>
+          <t>0.0062618595825426945 +/- 0.002979523267125593</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.007843137254901988 +/- 0.0010277088430912082</t>
+          <t>-0.0015496521189120593 +/- 0.0020663372832282825</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0026565464895635495 +/- 0.0008855154965211951</t>
+          <t>-0.004554079696394686 +/- 0.0010789830556123935</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.014579380139152453 +/- 0.002174817362043537</t>
+          <t>-0.010879190385831749 +/- 0.0010020859910028393</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0028779253636938896 +/- 0.00109964191339112</t>
+          <t>-0.009993674889310567 +/- 0.0016865644055627299</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00015812776723589383 +/- 0.000324065489119508</t>
+          <t>0.0005060088551549713 +/- 0.00015493293755741114</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0006008855154964965 +/- 0.0014315585449407146</t>
+          <t>0.002024035420619874 +/- 0.0016200187823992103</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.002593295382669214 +/- 0.001573669235246669</t>
+          <t>-0.004395951929158759 +/- 0.0011615665826822917</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0007590132827324347 +/- 0.0008741476888732204</t>
+          <t>0.0007906388361796357 +/- 0.0009618536575424233</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0020556609740670084 +/- 0.0010417248002530372</t>
+          <t>0.001486401012017724 +/- 0.00040128328717426077</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.002435167615433287 +/- 0.0013643045294195496</t>
+          <t>0.0018026565464895673 +/- 0.0017892909753087559</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.00015812776723590495 +/- 0.0004301540325343406</t>
+          <t>0.000727387729285256 +/- 0.0007078756889816305</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.002213788741302991 +/- 0.0022540834511328854</t>
+          <t>0.00028462998102465333 +/- 0.001359898798228972</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.001612903225806428 +/- 0.0016701765877939027</t>
+          <t>-0.008285895003162569 +/- 0.0030655587137387954</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.0007273877292852448 +/- 0.0009701367267664561</t>
+          <t>-0.0038583175205565865 +/- 0.0015736692352466355</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.00022137887413031798 +/- 0.0011837423954593927</t>
+          <t>-0.0030360531309297834 +/- 0.0018288212896648828</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.003573687539531978 +/- 0.0002470034685612392</t>
+          <t>0.0005376344086021612 +/- 0.00028462998102466195</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.00012650221378877058 +/- 0.00035216725887600604</t>
+          <t>-0.0010120177103099203 +/- 0.0006450372566214718</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.0017394054395952208 +/- 0.001032078992541477</t>
+          <t>3.162555344718987e-05 +/- 0.0018026565464895812</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.0005060088551549491 +/- 0.0014157513779632655</t>
+          <t>0.004174573055028474 +/- 0.0021111093318505617</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.0005060088551549158 +/- 0.0002898529851332093</t>
+          <t>-0.0007590132827324459 +/- 0.00037950664136621366</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.48766603415252e-05 +/- 0.0005666183702456798</t>
+          <t>0.0008538899430740043 +/- 0.000800695060162683</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.0032890575585072914 +/- 0.0015634670581035214</t>
+          <t>0.0034788108791903973 +/- 0.0014492649256659883</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.002530044275774823 +/- 0.0011662927839712657</t>
+          <t>-0.0013598987982289534 +/- 0.0014971284476337156</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.003858317520556609 +/- 0.0006899881160427421</t>
+          <t>0.0007906388361796468 +/- 0.0008031894433397028</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0018342820999367126 +/- 0.0006603609430051078</t>
+          <t>0.002403542061986097 +/- 0.0017676392931666065</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.001170145477545881 +/- 0.001476950591883062</t>
+          <t>-0.004174573055028452 +/- 0.0012394635004595541</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.002719797596457918 +/- 0.0012507096731995866</t>
+          <t>-0.0013915243516761434 +/- 0.0016261809148870846</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.001644528779253629 +/- 0.0012150140867994014</t>
+          <t>-0.007273877292852604 +/- 0.0016674796111909084</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.00224541429475017 +/- 0.001117684822711707</t>
+          <t>-0.006166982922201148 +/- 0.0017679221833489705</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0021189120809614105 +/- 0.0005666183702457009</t>
+          <t>-0.0019607843137254832 +/- 0.0013770740706563716</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.0036053130929791346 +/- 0.0006512100025924826</t>
+          <t>-0.006767868437697677 +/- 0.0007239420077330492</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0005376344086021279 +/- 0.00044836960400879833</t>
+          <t>0.0008855154965212054 +/- 0.0004647988126723135</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0037318153067678827 +/- 0.0007975661108740421</t>
+          <t>-0.004585705249841876 +/- 0.001437136972485999</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.001138519924098702 +/- 0.001050806307769527</t>
+          <t>-0.004332700822264402 +/- 0.0014837070342492052</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0037950664136622405 +/- 0.0010771275373767375</t>
+          <t>-0.010847564832384572 +/- 0.0014004800648630296</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.002118912080961444 +/- 0.0011494485670705903</t>
+          <t>0.006831119544592035 +/- 0.0009920548476507177</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.00044275774826061374 +/- 0.0004289898787555607</t>
+          <t>0.0005692599620493288 +/- 0.0004647988126723165</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.00044275774826061374 +/- 0.00032251862831071573</t>
+          <t>0.0011068943706514678 +/- 0.0004950182113377145</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.005692599620493366 +/- 0.0005099467266475901</t>
+          <t>-0.0017710309930423663 +/- 0.000695762175838068</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.0007906388361796246 +/- 0.0015765267021650448</t>
+          <t>-0.005660974067046165 +/- 0.0015262401659726246</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.0007590132827324681 +/- 0.0012346123526845911</t>
+          <t>-0.01410499683744466 +/- 0.0015311471773447286</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.00025300442757750783 +/- 0.00027570518301963656</t>
+          <t>-0.0002846299810246755 +/- 0.000411132194813423</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.009614168247944366 +/- 0.0013432486136366326</t>
+          <t>-0.015591397849462351 +/- 0.0010398027971393838</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.006451612903225834 +/- 0.0008967392080175779</t>
+          <t>-0.011733080328905732 +/- 0.0015777950263461528</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.00025300442757751894 +/- 0.0004858409707696683</t>
+          <t>-0.0006008855154965076 +/- 0.0008179960250712958</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.013187855787476287 +/- 0.0011230411704341988</t>
+          <t>-0.010879190385831761 +/- 0.0012100649253452985</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.0015496521189120927 +/- 0.001545774751404182</t>
+          <t>-0.002877925363693856 +/- 0.0019312314536080982</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.001992409867172662 +/- 0.0017948720586543649</t>
+          <t>-0.005154965211891183 +/- 0.0014004800648630515</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.002783048703352309 +/- 0.0007183944776470979</t>
+          <t>-0.003067678684376962 +/- 0.0018977967348105592</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.00018975332068313922 +/- 0.00015493293755746554</t>
+          <t>-0.00012650221378875947 +/- 0.00015493293755746551</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.0022770398481973706 +/- 0.001560906094782165</t>
+          <t>0.003700189753320682 +/- 0.0011230411704342101</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.0010120177103099203 +/- 0.0010469921162078824</t>
+          <t>-0.002118912080961399 +/- 0.00117526275623417</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.0007906388361796135 +/- 0.0008155469296791591</t>
+          <t>0.0025616698292220243 +/- 0.0008056761039125138</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.004111321948134072 +/- 0.0014072482897714781</t>
+          <t>0.00328905755850728 +/- 0.0015180265654648958</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0004743833017077925 +/- 0.0014509892153009823</t>
+          <t>-3.162555344717877e-05 +/- 0.00111768482271173</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.004111321948134117 +/- 0.0013712513212320403</t>
+          <t>-0.001644528779253618 +/- 0.0013915243516761514</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.00015812776723594935 +/- 0.00015812776723594935</t>
+          <t>9.487666034156961e-05 +/- 0.00014492649256661917</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.0010752688172043444 +/- 0.0010602817592814708</t>
+          <t>0.0007273877292852781 +/- 0.0009061700684310224</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.00044275774826062485 +/- 0.0005865666347562311</t>
+          <t>0.0012017710309930596 +/- 0.0008695589553995947</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.0005376344086021279 +/- 0.0004909606165800289</t>
+          <t>0.0006008855154965187 +/- 0.0006701334630112962</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0015875901831766076</t>
+          <t>-0.0032574320050600793 +/- 0.0008950646235347926</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0003162555344718099 +/- 0.00031625553447186535</t>
+          <t>0.001834282099936757 +/- 0.0006899881160427441</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0026881720430107616 +/- 0.0011684347376287863</t>
+          <t>0.0018975332068311367 +/- 0.0010000878115649487</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.0015812776723592493 +/- 0.001048900945716452</t>
+          <t>0.004269449715370033 +/- 0.0006519774866568059</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0035104364326375426 +/- 0.0010436432637571237</t>
+          <t>0.0023086654016445385 +/- 0.0008130904574435392</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0017394054395951542 +/- 0.00139475503296647</t>
+          <t>0.00224541429475017 +/- 0.001244697574582826</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0036685641998734806 +/- 0.0017042623131318972</t>
+          <t>-0.0001897533206831059 +/- 0.0015047915564035835</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.0011385199240986576 +/- 0.0006957621758380793</t>
+          <t>-0.00056925996204934 +/- 0.0010937138814541688</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.007151780137414054 +/- 0.0012370582336251401</t>
+          <t>-0.005902560899437781 +/- 0.0010859049750602018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0043098063710181435 +/- 0.002775123034543812</t>
+          <t>0.0023422860712055127 +/- 0.0019415716480161974</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.006589631480324732 +/- 0.0009206372875067943</t>
+          <t>0.0040287320424734815 +/- 0.0018761696809338779</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.0018425983760150034 +/- 0.001947590484405868</t>
+          <t>0.00306058713304187 +/- 0.0012319227310003845</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0029981261711429564 +/- 0.0008167830624997958</t>
+          <t>0.010899437851342942 +/- 0.0015264646358338124</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0018425983760150034 +/- 0.0020970983090817814</t>
+          <t>-0.0005933791380387076 +/- 0.0025350610710281737</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0002810743285446615 +/- 0.00032605579353249916</t>
+          <t>6.246096189881367e-05 +/- 0.0004996876951905093</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.0020299812617114443 +/- 0.0011453542049276936</t>
+          <t>-0.004747033104309762 +/- 0.0012785440031516694</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.004216114928169823 +/- 0.0019111931643715457</t>
+          <t>0.018363522798251118 +/- 0.003870060231020533</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.02045596502186129 +/- 0.0028733739732070933</t>
+          <t>0.031324172392254844 +/- 0.002892994602653528</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.004622111180512212 +/- 0.0010890440833330928</t>
+          <t>-0.004934415990006191 +/- 0.001395272198856233</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.006777014366021172 +/- 0.001410912804256914</t>
+          <t>-0.007339163023110495 +/- 0.0015816935992630464</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.00630855715178007 +/- 0.0011242973141786462</t>
+          <t>-0.0010618363522798325 +/- 0.0017173925152863976</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.019331667707682722 +/- 0.004200354562135466</t>
+          <t>-0.006121174266083651 +/- 0.0034838437894776585</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.0011555277951280196 +/- 0.002104526619466744</t>
+          <t>0.0024359775140537334 +/- 0.0025402497698517046</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0004372267332916957 +/- 0.0011867582760774597</t>
+          <t>-0.000374765771392882 +/- 0.0014767758173063047</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>6.246096189881367e-05 +/- 0.0010148705065129314</t>
+          <t>-0.0014053716427233076 +/- 0.0011368066660338177</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0005309181761399163 +/- 0.0008149899032292304</t>
+          <t>0.0009369144284822051 +/- 0.0014977612502538266</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.0050281074328544 +/- 0.0018761696809338592</t>
+          <t>0.006402248594628401 +/- 0.0008637924226070847</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00046845721424110254 +/- 0.0002517881870174455</t>
+          <t>0.00015615240474703418 +/- 0.000320017200685811</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00031230480949406836 +/- 0.001007152748069782</t>
+          <t>0.003247970018738311 +/- 0.001446075815464123</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.005277951280449644 +/- 0.000982147732262117</t>
+          <t>-0.0009369144284822051 +/- 0.0012255725715395827</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.002217364147407819 +/- 0.0012834929786404716</t>
+          <t>0.004497189256714584 +/- 0.001136377601415389</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.003091817613991199 +/- 0.0012370582336251048</t>
+          <t>-0.002841973766396 +/- 0.0012211876824495217</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0006246096189881367 +/- 0.0008023255826774027</t>
+          <t>-0.0014053716427233076 +/- 0.001203488374016104</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0005309181761399163 +/- 0.00042016314950261724</t>
+          <t>-0.000374765771392882 +/- 0.0008811202985425348</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.015115552779512797 +/- 0.0013555611751537074</t>
+          <t>0.0027170518425983945 +/- 0.0014246714213562925</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.024328544659587704 +/- 0.0024923802252003638</t>
+          <t>0.00424734540911933 +/- 0.001250779787289252</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.001717676452217376 +/- 0.0012743413968209435</t>
+          <t>-0.003747657713928776 +/- 0.0009369144284821606</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.006058713304184815 +/- 0.0004878357074270274</t>
+          <t>-0.010805746408494655 +/- 0.0017897000352148035</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.000187382885696441 +/- 0.000579239131511291</t>
+          <t>-0.0006246096189881367 +/- 0.0004190008702373151</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.123048094940684e-05 +/- 0.00038121660261504644</t>
+          <t>-0.00046845721424110254 +/- 0.0003760647900934534</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.246096189881367e-05 +/- 0.0011155884509364067</t>
+          <t>-0.007214241099312868 +/- 0.0013356280312519203</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.0013429106808244494 +/- 0.001347261374773417</t>
+          <t>-0.00012492192379762735 +/- 0.0015627727674199737</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0008744534665833803 +/- 0.0008119925046845555</t>
+          <t>-0.0006246096189881367 +/- 0.0006246096189881367</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-9.36914428482205e-05 +/- 0.00028107432854466156</t>
+          <t>-0.0014678326046221213 +/- 0.0005767078486139762</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0018113678950655964 +/- 0.0014229588694434224</t>
+          <t>-0.0027795128044971864 +/- 0.0026442831806057832</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0.0029981261711429785 +/- 0.0014119493510876956</t>
+          <t>-0.007307932542161088 +/- 0.00117020574610839</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0004059962523422889 +/- 0.0005595400645586833</t>
+          <t>0.0018113678950655964 +/- 0.0003642068641377477</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.0009993753903810188 +/- 0.0010800509972386447</t>
+          <t>0.0008744534665833914 +/- 0.0010618363522798325</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0033104309806370248 +/- 0.0010655041917071676</t>
+          <t>-0.00593379138038721 +/- 0.0019652882851408046</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.0029356652092442427 +/- 0.0013042231741299966</t>
+          <t>-0.0002498438475952547 +/- 0.0018675723157684143</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.006058713304184926 +/- 0.0013338011557815597</t>
+          <t>0.006933166770768317 +/- 0.0014297967698013337</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.014022485946283603 +/- 0.002083098831436857</t>
+          <t>-0.011024359775140501 +/- 0.0013759144766964922</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.003935040599625151 +/- 0.0010282372038197653</t>
+          <t>0.0013116801998750871 +/- 0.000995463925703269</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0013741411617739009 +/- 0.000741682828671955</t>
+          <t>0.0036539662710805996 +/- 0.0008385834842034757</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.00012492192379762735 +/- 0.0005074352532564657</t>
+          <t>0.0005933791380387299 +/- 0.0004293481288215994</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.0034978138663334657 +/- 0.0011584782630225602</t>
+          <t>-0.003185509056839453 +/- 0.0015414069555593738</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.004465958775765178 +/- 0.0014980868151419787</t>
+          <t>0.007432854465958827 +/- 0.0013952721988562667</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.002873204247345351 +/- 0.0012476567367543882</t>
+          <t>0.002092442223610258 +/- 0.0014246714213562925</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.01705184259837602 +/- 0.0017897000352148035</t>
+          <t>-0.012304809494066182 +/- 0.0024598836561543227</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.00021861336664584784 +/- 0.0004427684846582737</t>
+          <t>-3.123048094940684e-05 +/- 0.0004059962523422889</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.0005933791380387299 +/- 0.00035471007781388587</t>
+          <t>-0.0003435352904434752 +/- 0.00042934812882159946</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-6.246096189881367e-05 +/- 0.00012492192379762735</t>
+          <t>-0.00046845721424110254 +/- 0.0002879308075356949</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.0069643972517177246 +/- 0.0011772690084304119</t>
+          <t>-0.008119925046845666 +/- 0.0015489814825280866</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.0004059962523422889 +/- 0.0014784260310486829</t>
+          <t>0.008525921299188065 +/- 0.0009163898033180082</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0005933791380387299 +/- 0.000631597389636378</t>
+          <t>-0.00021861336664584784 +/- 0.0008615311820196013</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.0009369144284822051 +/- 0.0010451718007921066</t>
+          <t>-0.003841349156776974 +/- 0.001193723601100304</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.002311055590256106 +/- 0.001816744481230367</t>
+          <t>0.011773891317926333 +/- 0.0012018664212925198</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0014366021236726922 +/- 0.0004236308546611296</t>
+          <t>0.0 +/- 0.0005409277974918454</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0003435352904434752 +/- 0.0009311712377186556</t>
+          <t>0.003685196752030007 +/- 0.0007230379077320616</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.005777638975640265 +/- 0.0013487084873010202</t>
+          <t>0.00424734540911933 +/- 0.001250779787289252</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0035290443472829726 +/- 0.0018740890929016367</t>
+          <t>-0.011680199875078045 +/- 0.001194948561505879</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.0061524047470331465 +/- 0.0011605811477865195</t>
+          <t>-0.0008432229856339846 +/- 0.001471814074696847</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-9.36914428482205e-05 +/- 0.0002439178537135137</t>
+          <t>-9.36914428482205e-05 +/- 0.00034353529044347516</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0006400344013716221</t>
+          <t>0.0023735165521549194 +/- 0.0013483468547734574</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0025608994378513604 +/- 0.0008811202985425348</t>
+          <t>-0.00996252342286067 +/- 0.0017746499244441563</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.246096189881367e-05 +/- 0.0004372267332916957</t>
+          <t>-0.0004996876951905094 +/- 0.0006430749619604666</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.006121174266083629 +/- 0.0011449283435242652</t>
+          <t>-0.0011867582760774487 +/- 0.001381220761242706</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.00306058713304187 +/- 0.0008586962576431989</t>
+          <t>0.0028732042473454287 +/- 0.0009348300778948075</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.0006870705808869504 +/- 0.0009348300778948076</t>
+          <t>0.001124297314178646 +/- 0.0014050245945286784</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-3.123048094940684e-05 +/- 0.00016818128691863026</t>
+          <t>0.00021861336664584784 +/- 0.000541828593781936</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0004372267332916957 +/- 0.0004460604889783197</t>
+          <t>0.001124297314178646 +/- 0.0009072978792213648</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0017801374141161563 +/- 0.00044276848465822746</t>
+          <t>0.0011867582760774597 +/- 0.0005892555360435146</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,52 +3491,52 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.00015615240474703418 +/- 0.0007807620237351709</t>
+          <t>0.0012179887570268667 +/- 0.0004928086770162277</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0013429106808244607 +/- 0.000988088196099679</t>
+          <t>0.0013116801998750871 +/- 0.001207937514416855</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-3.123048094940684e-05 +/- 9.369144284822049e-05</t>
+          <t>-0.000187382885696441 +/- 0.00020715957466304951</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0004059962523422889 +/- 0.0005235182577838952</t>
+          <t>-0.00046845721424110254 +/- 0.0005272311997543489</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.0022173641474078853 +/- 0.001001812300583732</t>
+          <t>-0.0004059962523422889 +/- 0.001117772027993342</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.004653341661461507 +/- 0.001180578274293312</t>
+          <t>0.000749531542785764 +/- 0.0010926205924132431</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0.0009681449094316119 +/- 0.0005309181761399161</t>
+          <t>-0.0014053716427233076 +/- 0.0008524262375987679</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.003841349156777041 +/- 0.0008615311820196012</t>
+          <t>0.0043098063710181435 +/- 0.0016155549227205063</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0008432229856339846 +/- 0.0018266494460824308</t>
+          <t>-0.003747657713928765 +/- 0.0015426719594288769</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0007807620237351709 +/- 0.0011107694718162939</t>
+          <t>0.0016864459712679692 +/- 0.0008744534665833915</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.001791326209930877 +/- 0.00225332391832097</t>
+          <t>0.0019798868636077827 +/- 0.0017891194629151745</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.004211187932118188 +/- 0.001963607712358673</t>
+          <t>0.0062225015713387784 +/- 0.0013318428724335134</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0031112507856693727 +/- 0.001829513460443479</t>
+          <t>0.0009113764927718537 +/- 0.0025198317140667803</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.00012570710245130012 +/- 0.0013124206799384878</t>
+          <t>-0.007605279698302958 +/- 0.002059832760298416</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0022941546197359996 +/- 0.0021911022015780536</t>
+          <t>0.003236957888120695 +/- 0.0018753650217266655</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0009113764927718204 +/- 0.00166561910747958</t>
+          <t>0.006316781898177248 +/- 0.0021473941302145288</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0001571338780640974 +/- 0.0005305450350764917</t>
+          <t>-0.00018856065367695019 +/- 0.00044886413755769277</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.00113136392206159 +/- 0.0015975191737446803</t>
+          <t>0.006599622878692646 +/- 0.0020511840191176156</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.016404776869893133 +/- 0.002706354511830427</t>
+          <t>0.004745443117536119 +/- 0.0037302669226107177</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.012979258328095522 +/- 0.0037896313276904415</t>
+          <t>0.01681332495285982 +/- 0.002538575490478251</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.004305468258956657 +/- 0.001997764308650264</t>
+          <t>-0.0021998742928975522 +/- 0.0017270435781312331</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0004714016341923477 +/- 0.0017112449264691406</t>
+          <t>0.0023884349465744803 +/- 0.0018227529855436662</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0003456945317410476 +/- 0.0018616220263507068</t>
+          <t>0.008139534883720934 +/- 0.0016537174251317292</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.01825895663104964 +/- 0.0016296533202343401</t>
+          <t>0.019044626021370203 +/- 0.0015913248147293676</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.029918290383406643 +/- 0.0029807431053122026</t>
+          <t>0.013544940289126317 +/- 0.0032277914796252864</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.005342551854179778 +/- 0.0016147369677768776</t>
+          <t>0.004525455688246372 +/- 0.002099722575548719</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.007416719044626008 +/- 0.00105361751189443</t>
+          <t>0.009050911376492776 +/- 0.001465984134467713</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0021684475172847107 +/- 0.001529615779212808</t>
+          <t>0.004148334380892527 +/- 0.0015888403092098656</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.00609679446888749 +/- 0.001515018327239962</t>
+          <t>0.0026712759270898665 +/- 0.0015022524704861222</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00040854808296668653 +/- 0.0005268087559472321</t>
+          <t>-0.0009113764927718537 +/- 0.0004543316246009011</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.005562539283469492 +/- 0.0021177543166350076</t>
+          <t>-0.003614079195474551 +/- 0.0022233194413355316</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.005468258956631078 +/- 0.0015788631913363329</t>
+          <t>-0.00025141420490258913 +/- 0.0009086632492018114</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.004116907605279718 +/- 0.0020629470059429647</t>
+          <t>0.010150848522941536 +/- 0.00195781497513167</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0021998742928975744 +/- 0.0015137139633931364</t>
+          <t>0.00018856065367692799 +/- 0.001312420679938475</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.009553739786297954 +/- 0.0016159597903434722</t>
+          <t>-0.005782526712759273 +/- 0.00130487363243413</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0011313639220616122 +/- 0.0007850406031927553</t>
+          <t>0.0019484600879949854 +/- 0.0004399748585795187</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.003645505971087382 +/- 0.002718733972832459</t>
+          <t>0.0028284098051539865 +/- 0.0024057396868642058</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.005405405405405428 +/- 0.001563778165257682</t>
+          <t>0.0009113764927718316 +/- 0.0009982639958685461</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.002325581395348819 +/- 0.0017733169050491266</t>
+          <t>-0.0023255813953488302 +/- 0.0011261139451394532</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.006631049654305443 +/- 0.0014837299351493436</t>
+          <t>-0.004839723444374588 +/- 0.0008098113593164763</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.003268384663733537 +/- 0.0005656819610307864</t>
+          <t>-0.00018856065367693907 +/- 0.00037712130735386893</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.1426775612852786e-05 +/- 0.0004320467342824584</t>
+          <t>0.0009428032683846399 +/- 0.0008777020769182215</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.008768070395977379 +/- 0.0014568607148333532</t>
+          <t>0.003928346951602757 +/- 0.001489045599054946</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.00106851037083594 +/- 0.0021962797246582208</t>
+          <t>0.004682589566310491 +/- 0.0014568607148333337</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.002514142049025814 +/- 0.0006885261565118447</t>
+          <t>0.0009113764927718316 +/- 0.0006355672035247167</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00018856065367691687 +/- 0.0009957875246860344</t>
+          <t>-0.00040854808296670876 +/- 0.0007575091636200057</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.009962287869264608 +/- 0.0019578149751316646</t>
+          <t>0.0009742300439974705 +/- 0.0020437071637824326</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.00021998742928978077 +/- 0.0023477715519320884</t>
+          <t>0.0012570710245128792 +/- 0.0011066509655348292</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0009742300439974927 +/- 0.0011017314986145885</t>
+          <t>0.000125707102451289 +/- 0.0011084344493116592</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.005311125078566947 +/- 0.002096191847347877</t>
+          <t>-0.0017598994343180463 +/- 0.001099488100850784</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.002357008170961661 +/- 0.0013127968934132713</t>
+          <t>-0.0009428032683846621 +/- 0.0008432688790068092</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0005971087366436145 +/- 0.0026460150672270996</t>
+          <t>0.0054368321810182255 +/- 0.0008201124041923268</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.009365179132621016 +/- 0.0026286013408330067</t>
+          <t>-0.013513513513513532 +/- 0.0018803614458392833</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.0022627278441231915 +/- 0.0015574496157591264</t>
+          <t>-0.006662476429918296 +/- 0.001021249328049791</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.0056253928346951644 +/- 0.001735315863265676</t>
+          <t>-0.00260842237586425 +/- 0.0010236642033251144</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.006945317410433682 +/- 0.0020677289942923954</t>
+          <t>0.002734129478315539 +/- 0.0019118744405097743</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0001571338780641196 +/- 0.0009242891998650387</t>
+          <t>-0.0013199245757385292 +/- 0.0009301476170300949</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.006913890634820885 +/- 0.0016390200893029836</t>
+          <t>0.0011627906976744208 +/- 0.0014676674329146056</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.0010056568196103344 +/- 0.0015763590451268912</t>
+          <t>-0.0013827781269641793 +/- 0.002080822797894015</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.007919547454431186 +/- 0.0017877388627690442</t>
+          <t>-0.004808296668761802 +/- 0.0014541464866447901</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.013073538654934025 +/- 0.001953522346690141</t>
+          <t>-0.0010685103708359734 +/- 0.001566302425440229</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0018541797611564936 +/- 0.0008485229415461889</t>
+          <t>-0.0014142049025769876 +/- 0.00044996294982008634</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.0007542426147077342 +/- 0.0009655745754706021</t>
+          <t>-0.0001571338780641196 +/- 0.0004919068460873143</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.00021998742928974746 +/- 0.00020122954863083052</t>
+          <t>0.0007228158390948924 +/- 0.00048787475475362235</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.009805153991200511 +/- 0.0019716388612643757</t>
+          <t>-0.007196731615336271 +/- 0.0009370239796276486</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.006033940917661828 +/- 0.0024415995725399382</t>
+          <t>-0.000754242614707723 +/- 0.0013495229763409058</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0027341294783155058 +/- 0.0008201124041923312</t>
+          <t>0.0010999371464487594 +/- 0.00066294855781676</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.003299811439346301 +/- 0.0014487027745588952</t>
+          <t>0.0028284098051539973 +/- 0.0009532213003207629</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.002105593966059105 +/- 0.0030985270812589013</t>
+          <t>-0.0008170961659333842 +/- 0.002518851654244356</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.0007856693903205647 +/- 0.0006166378651901006</t>
+          <t>-0.0013199245757385292 +/- 0.0008170961659333748</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.006945317410433705 +/- 0.0014294865387233394</t>
+          <t>0.004431175361407913 +/- 0.0014363789920837614</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.012790697674418617 +/- 0.001896313619301756</t>
+          <t>0.0007542426147077119 +/- 0.0022186502318947486</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0.008453802639849118 +/- 0.0023027485985823142</t>
+          <t>0.013262099308610931 +/- 0.0008640934685649055</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.004242614707730974 +/- 0.0015603006395105386</t>
+          <t>-3.1426775612852786e-05 +/- 0.001436378992083776</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-0.00037712130735385597 +/- 0.00043997485857950923</t>
+          <t>-0.0003456945317410587 +/- 0.0004085480829667011</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.0025455688246385777 +/- 0.0016113694209043633</t>
+          <t>0.0038969201759899374 +/- 0.0018918814510738326</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.00524827152734132 +/- 0.0016513267951501734</t>
+          <t>0.0012256442489000485 +/- 0.0011017314986145903</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0020741671904462855 +/- 0.0010904683578188373</t>
+          <t>0.0027027027027027085 +/- 0.0006158365160988519</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.017693274670018844 +/- 0.0013557293909568133</t>
+          <t>0.015901948460087988 +/- 0.002846509584971525</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0006285355122564673 +/- 0.001264903318510253</t>
+          <t>0.002514142049025769 +/- 0.0016806715219511083</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.012476429918290366 +/- 0.002046604670668123</t>
+          <t>0.010590823381521041 +/- 0.001896313619301771</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-9.428032683845844e-05 +/- 0.0005630569725697294</t>
+          <t>-0.00040854808296668653 +/- 0.0002454509640448585</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.0016341923318667795 +/- 0.0007672253686821974</t>
+          <t>-9.428032683846954e-05 +/- 0.0009537392146758886</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0007228158390949369 +/- 0.0007831512127201149</t>
+          <t>-0.00040854808296669765 +/- 0.0004878747547536224</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.0037712130735386706 +/- 0.0006126206376372582</t>
+          <t>0.0003142677561282059 +/- 0.0013333251687992831</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.0013827781269641793 +/- 0.001687708558403212</t>
+          <t>0.005342551854179778 +/- 0.0015900830472248139</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0009113764927718759 +/- 0.0002610504042400181</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.000993801904515526</t>
+          <t>-0.0004714016341923477 +/- 0.0007981411124575754</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.004148334380892538 +/- 0.0027854833194418944</t>
+          <t>0.003236957888120673 +/- 0.0012416559563254972</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.005688246385920803 +/- 0.002233070889187993</t>
+          <t>0.0009113764927718316 +/- 0.0015231452942869427</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0021998742928975856 +/- 0.0007302922714407455</t>
+          <t>-0.0009742300439974927 +/- 0.0004320467342824464</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.002859836580766806 +/- 0.0017968312204805345</t>
+          <t>0.0012884978001257096 +/- 0.0013067644805966002</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.006599622878692635 +/- 0.00165699890967494</t>
+          <t>0.010810810810810811 +/- 0.0022627278441231984</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0034569453174104537 +/- 0.0015202245911310887</t>
+          <t>-0.0005656819610308061 +/- 0.0009086632492018283</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0014008941877794335 +/- 0.0009239940387481198</t>
+          <t>-0.0006259314456036113 +/- 0.0012607025921047039</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.005096870342771964 +/- 0.0025024835467722497</t>
+          <t>-0.005096870342772009 +/- 0.0017906096328912696</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0029806259314455797 +/- 0.0008841965409354034</t>
+          <t>0.002324888226527544 +/- 0.0012978563968451648</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0005067064083457362 +/- 0.0007059743238346864</t>
+          <t>0.002414307004470906 +/- 0.001775662713395719</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.0003278688524590012 +/- 0.0006027942896022822</t>
+          <t>0.0016393442622950505 +/- 0.0014185399742820714</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.0003278688524590012 +/- 0.0008887064987109229</t>
+          <t>-0.004739195230998539 +/- 0.0010866006636994496</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.00011922503725781963 +/- 0.00035767511177346815</t>
+          <t>0.0008345752608047263 +/- 0.00034759772845574055</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0018777943368107452 +/- 0.0011392855352379402</t>
+          <t>-0.0006855439642325378 +/- 0.001006816438393715</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.0023845007451564924 +/- 0.0029295171088657163</t>
+          <t>0.0005365126676601717 +/- 0.00277310363031012</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.00023845007451563926 +/- 0.0023688007733300032</t>
+          <t>0.004292101341281651 +/- 0.0023740456335904505</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.00470938897168407 +/- 0.001205588579204579</t>
+          <t>0.004947839046199687 +/- 0.001655254053879554</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.0007153502235469289 +/- 0.0010763320468117794</t>
+          <t>0.0054843517138598915 +/- 0.001959974035502088</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.007660208643815214 +/- 0.0016053929072423606</t>
+          <t>0.006706408345752568 +/- 0.0019961294366918907</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.023427719821162464 +/- 0.0026964370498714927</t>
+          <t>0.02554396423248879 +/- 0.0017686442562321113</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013532041728763067 +/- 0.0014674853800406716</t>
+          <t>0.006080476900149001 +/- 0.0017287630402384486</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.004083457526080458 +/- 0.0006399675276776134</t>
+          <t>-0.002891207153502251 +/- 0.0012995665786343835</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.0011922503725782297 +/- 0.00107467996288049</t>
+          <t>-0.0005961251862891537 +/- 0.001423229375417383</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.005543964232488841 +/- 0.0013005916083023228</t>
+          <t>0.004172876304023821 +/- 0.0010746799628804685</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.0012816691505215915 +/- 0.001170061783987516</t>
+          <t>-0.003785394932935937 +/- 0.0014359689383542022</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-8.941877794337305e-05 +/- 0.0001365894394919849</t>
+          <t>0.00020864381520118157 +/- 0.0002682563338300871</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00712369597615502 +/- 0.0013226055280079853</t>
+          <t>-0.0025335320417288034 +/- 0.002400283090943467</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0035767511177347442 +/- 0.0015602089214071303</t>
+          <t>0.007511177347242904 +/- 0.0018652146464574703</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0035767511177347334 +/- 0.0011310680155594782</t>
+          <t>0.004441132637853928 +/- 0.0012249611080795558</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.004411326378539493 +/- 0.0009500672101645007</t>
+          <t>0.00539493293591653 +/- 0.001456852388655733</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0014605067064083267 +/- 0.0011188270866839707</t>
+          <t>0.009955290611028279 +/- 0.0013276338272023812</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00038748137108793876 +/- 0.0006399675276776284</t>
+          <t>0.0006855439642324601 +/- 0.000933559449380978</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.003517138599105829 +/- 0.0015244961970246585</t>
+          <t>0.0020864381520118934 +/- 0.001435659562300105</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.002503725782414312 +/- 0.0011635899431262544</t>
+          <t>0.0007451564828613644 +/- 0.0015095627138122778</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0022354694485842153 +/- 0.0008561196194542333</t>
+          <t>-0.0007153502235469622 +/- 0.0011712001612153979</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0067660208643815275 +/- 0.002065253317594045</t>
+          <t>0.005871833084947808 +/- 0.0016273780858084858</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0002682563338301192 +/- 0.0008265528836877541</t>
+          <t>-0.0008047690014903464 +/- 0.0004996439527344382</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.0005961251862890982 +/- 0.0007657366663883825</t>
+          <t>-0.0007749627421758887 +/- 0.0006691488620162194</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.0045007451564828774 +/- 0.0011730950017379861</t>
+          <t>0.0013412816691504737 +/- 0.0015387075408811054</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.0030402384500745395 +/- 0.0008409380613809784</t>
+          <t>0.0024143070044709168 +/- 0.0020626706738356</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.003755588673621446 +/- 0.0003817063628872252</t>
+          <t>-0.0032190760059612744 +/- 0.000950067210164468</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0011922503725782518 +/- 0.0011388955692722767</t>
+          <t>0.0013412816691504958 +/- 0.001034667955750215</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.003129657228017879 +/- 0.0012663276176600943</t>
+          <t>0.0032488822652756875 +/- 0.0017955642899349018</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0057526080476900335 +/- 0.0009890110296892584</t>
+          <t>0.0013710879284649425 +/- 0.0011168401785511318</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.00038748137108793876 +/- 0.000832976966466888</t>
+          <t>0.0018777943368107008 +/- 0.0010914952860566665</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0023546944858420125 +/- 0.0010190951414174988</t>
+          <t>0.0029508196721311332 +/- 0.0015797317436661742</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0018181818181818299 +/- 0.0013158712402172267</t>
+          <t>0.0033681073025335073 +/- 0.0014846389753099725</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0016095380029806038 +/- 0.001838348011339402</t>
+          <t>0.0011624441132637498 +/- 0.0010617891583044427</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.007868852459016362 +/- 0.0017028741409342257</t>
+          <t>-0.006974664679582743 +/- 0.0011937397552608561</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.012011922503725792 +/- 0.0009143285633489089</t>
+          <t>0.01523099850968702 +/- 0.001180643953522403</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0010432190760059413 +/- 0.001230749497589447</t>
+          <t>0.008286140089418758 +/- 0.0012840929495402718</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0023845007451564924 +/- 0.001490312965722811</t>
+          <t>0.007332339791356146 +/- 0.001178761247885854</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.00023845007451565037 +/- 0.0004951787697715685</t>
+          <t>-0.00014903129657229953 +/- 0.0004054089570412969</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0006855439642324823 +/- 0.0015201192250372704</t>
+          <t>0.004977645305514133 +/- 0.000653702301027163</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.00178837555886735 +/- 0.0013329764396421938</t>
+          <t>-0.006408345752608058 +/- 0.0016009596425628344</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.002414307004470928 +/- 0.0013022981982088605</t>
+          <t>-0.00748137108792849 +/- 0.0011188270866839543</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.00324888226527571 +/- 0.00109474620996762</t>
+          <t>-0.007093889716840551 +/- 0.0012771556057006599</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0006557377049180247 +/- 0.000797561142191333</t>
+          <t>-0.0010730253353204654 +/- 0.0004842943907383687</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.0017287630402384568 +/- 0.0007975611421913438</t>
+          <t>-0.001400894187779478 +/- 0.0005340230362792453</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.00014903129657228842 +/- 0.00019994646594634097</t>
+          <t>0.00011922503725781963 +/- 0.0003319084568005998</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.004232488822652747 +/- 0.001483142212175827</t>
+          <t>-0.009329359165424767 +/- 0.0018520699115238052</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.003874813710879277 +/- 0.0012433176521379607</t>
+          <t>-0.004649776453055176 +/- 0.002146050670640825</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0006557377049180135 +/- 0.0010812731533363326</t>
+          <t>-0.0009239940387481771 +/- 0.0008157336621999621</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0023845007451564924 +/- 0.0010910882395065672</t>
+          <t>0.003368107302533496 +/- 0.0014665770015073257</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.009001490312965687 +/- 0.001726706212573502</t>
+          <t>-0.021877794336810773 +/- 0.0015556468972518398</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.002324888226527555 +/- 0.0008921984826882821</t>
+          <t>-0.0005067064083457917 +/- 0.0006803405192556577</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.003994038748137097 +/- 0.000990357539543138</t>
+          <t>0.003964232488822628 +/- 0.0010500098333119875</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.00742175856929953 +/- 0.0011578494545189217</t>
+          <t>-0.008196721311475452 +/- 0.0008867049049563969</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.008852459016393454 +/- 0.0015661764119725304</t>
+          <t>0.008584202682563324 +/- 0.001620539757862073</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.0033681073025335407 +/- 0.001066797625524484</t>
+          <t>0.0066467958271236634 +/- 0.001147057013704534</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.0002682563338301192 +/- 0.00033853402955592176</t>
+          <t>0.00011922503725780853 +/- 0.000303965395743218</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.0017585692995529146 +/- 0.0011578494545189163</t>
+          <t>0.0021460506706407977 +/- 0.0018460640914696857</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.001162444113263794 +/- 0.0011955988745234764</t>
+          <t>-0.001102831594634901 +/- 0.0010156020886677003</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.0008941877794336639 +/- 0.0008535213748599958</t>
+          <t>-0.0027421758569299848 +/- 0.0007516852585942408</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.0008941877794337083 +/- 0.0016966020233392086</t>
+          <t>0.002771982116244409 +/- 0.0018711590003838293</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.0031296572280178903 +/- 0.001723874067471981</t>
+          <t>0.000774962742175822 +/- 0.0009254351532792951</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.004113263785394938 +/- 0.0012771556057006646</t>
+          <t>-0.0019672131147541404 +/- 0.0007203008031948996</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>2.9806259314457682e-05 +/- 0.00033853402955592176</t>
+          <t>-0.00011922503725783073 +/- 0.0003319084568006158</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.002265275707898673 +/- 0.0007680535753636476</t>
+          <t>0.000953800298062546 +/- 0.0004951787697715752</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.0005365126676602494 +/- 0.0005931370713005246</t>
+          <t>0.0006557377049180024 +/- 0.0005623833759795204</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.001192250372578274 +/- 0.000788599496591538</t>
+          <t>0.0010730253353203767 +/- 0.0005023040103234829</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0013412816691505513 +/- 0.0014677880479577042</t>
+          <t>0.005394932935916519 +/- 0.0016240992817675584</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.00038748137108793876 +/- 0.00032786885245900723</t>
+          <t>-0.00011922503725783073 +/- 0.0001977123571001838</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.0004172876304023965 +/- 0.0002731788789839504</t>
+          <t>0.00047690014903125635 +/- 0.00033190845680057193</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.001192250372578274 +/- 0.0011466696907106583</t>
+          <t>-0.001281669150521647 +/- 0.0007184483334243532</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0034873323397913492 +/- 0.001214765059452436</t>
+          <t>-0.0039046199701937567 +/- 0.0008581925513494952</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.000894187779433675 +/- 0.0009040686073384883</t>
+          <t>0.0001490312965722551 +/- 0.0005031875712707556</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0014008941877794335 +/- 0.0012719277671148705</t>
+          <t>0.0019970193740685314 +/- 0.0014605067064083503</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.0014008941877794445 +/- 0.001372706878052982</t>
+          <t>-0.0033979135618480093 +/- 0.0011937397552608511</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.003010432190760093 +/- 0.0014260356141765377</t>
+          <t>0.0036959761549925307 +/- 0.0010512782169030293</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0036611195158849476 +/- 0.0009320981422541309</t>
+          <t>-0.003086232980332859 +/- 0.0008748461297912921</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.006596066565809333 +/- 0.0009355294906953377</t>
+          <t>-0.008350983358547637 +/- 0.0008472012102874293</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.003025718608169381 +/- 0.0012401755843823874</t>
+          <t>-0.006021180030257245 +/- 0.0005488156474195834</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.0007261724659606616 +/- 0.0007311979409134246</t>
+          <t>-0.0011195158850227037 +/- 0.0006772474821664027</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0005446293494704935 +/- 0.0008428676718416851</t>
+          <t>0.0011800302571860933 +/- 0.0008816219234089929</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.0035098335854764962 +/- 0.0015019272188793557</t>
+          <t>-0.002481089258698965 +/- 0.0012679169040700252</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.0003630862329803364 +/- 0.00012102874432677878</t>
+          <t>0.0005143721633888099 +/- 0.00013865584553573025</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0033888048411497063 +/- 0.0012751169443694654</t>
+          <t>-0.005900151285930466 +/- 0.0008033838455281019</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.009712556732223931 +/- 0.0019815569537104645</t>
+          <t>0.006172465960665607 +/- 0.0016472807974361675</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.01092284417549173 +/- 0.0024523257994495634</t>
+          <t>0.01095310136157337 +/- 0.0015593462906777914</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.0005446293494704935 +/- 0.0012822765567574498</t>
+          <t>-0.000605143721633894 +/- 0.0008118854986383583</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0003328290468986417 +/- 0.0010778525343756156</t>
+          <t>-0.0060816944024206345 +/- 0.0009320981422541309</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.0007261724659606506 +/- 0.0013409089141397889</t>
+          <t>-0.004841149773071152 +/- 0.0008341330561022908</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.005234493192133071 +/- 0.0020163639433036368</t>
+          <t>0.00021180030257186288 +/- 0.0019234148351362148</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.0023298033282904917 +/- 0.0016296802432067003</t>
+          <t>0.002450832072617248 +/- 0.001906202723146724</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.006777609682299501 +/- 0.0008893760034311171</t>
+          <t>-0.0009379727685325356 +/- 0.0009122428702984256</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.00211800302571854 +/- 0.0010740235612283482</t>
+          <t>-0.003963691376702006 +/- 0.0008169440242057569</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.004145234493192174 +/- 0.0008124491123811004</t>
+          <t>0.0017246596066565977 +/- 0.000766050765577748</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0013918305597579229 +/- 0.0013063257576352476</t>
+          <t>0.0006656580937972834 +/- 0.0010976312948391667</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.00042360060514372576 +/- 0.0002773116910714605</t>
+          <t>-3.02571860816947e-05 +/- 0.00016293993365006223</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.01624810892586983 +/- 0.0016240528774970982</t>
+          <t>-0.005839636913767066 +/- 0.001048576305667974</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0005446293494705045 +/- 0.0008319350732143816</t>
+          <t>-0.0009077155824508409 +/- 0.0008341330561022908</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0031467473524962484 +/- 0.0005929173356207447</t>
+          <t>0.0011497730711043986 +/- 0.0006601338647283402</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0014220877458396507 +/- 0.0009855671694343413</t>
+          <t>0.002208774583963713 +/- 0.0008669621048045109</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0036308623298033638 +/- 0.0008769365655787946</t>
+          <t>0.0014220877458396507 +/- 0.0009182445328589208</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0001512859304084735 +/- 0.00024394123292885412</t>
+          <t>0.0001210287443267788 +/- 0.00024205748865355762</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.006989409984871464 +/- 0.0017717901327633599</t>
+          <t>0.006989409984871364 +/- 0.0009892758078228123</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.002541603630862277 +/- 0.001014405725521317</t>
+          <t>-0.0010590015128593144 +/- 0.0010590015128593144</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.0002420574886535576 +/- 0.0007630571989663306</t>
+          <t>-0.00039334341906203105 +/- 0.0008236403987180837</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0013463597858569796</t>
+          <t>-0.0018759455370650712 +/- 0.0008319350732143816</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0006354009077155886 +/- 0.0003933434190620311</t>
+          <t>0.0008169440242057569 +/- 0.0004289696483739172</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.0001210287443267788 +/- 0.0004916210834878087</t>
+          <t>3.02571860816947e-05 +/- 0.00039334341906203105</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.002329803328290414 +/- 0.0010829367726579659</t>
+          <t>-0.0036308623298033638 +/- 0.0007286895357816891</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0014826021180029847 +/- 0.0007343213978524007</t>
+          <t>-0.002390317700453881 +/- 0.001111308179861249</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.0003328290468986417 +/- 0.00016293993365006223</t>
+          <t>-0.0001815431164901682 +/- 0.00014822933390518618</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0013615733736762614 +/- 0.0001512859304084735</t>
+          <t>-0.001301059001512872 +/- 0.00023631617778840334</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.0019667170953101554 +/- 0.000652461683898579</t>
+          <t>0.00553706505295003 +/- 0.0014639601093377104</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>6.05143721633894e-05 +/- 0.0007630571989663306</t>
+          <t>-0.0007261724659606728 +/- 0.0008685446350624789</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0002420574886535576 +/- 0.000570891445207667</t>
+          <t>0.000302571860816947 +/- 0.00046874231119000965</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.005506807866868435 +/- 0.000915748620297834</t>
+          <t>0.00239031770045387 +/- 0.0011596833825559241</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0007261724659606728 +/- 0.0005446293494705045</t>
+          <t>-0.0015733736762481242 +/- 0.0007134539257217375</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.000514372163388821 +/- 0.0009281610680894195</t>
+          <t>0.0029954614220877307 +/- 0.001103039402938438</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.0015733736762481242 +/- 0.0013517886779841994</t>
+          <t>0.0027231467473524894 +/- 0.0012253226463731378</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0007261724659606616 +/- 0.0010671825772192636</t>
+          <t>-0.005052950075643015 +/- 0.0006635918971092745</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0008472012102874515 +/- 0.0009157486202978338</t>
+          <t>0.0005748865355521993 +/- 0.000669087576021065</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.003903177004538616 +/- 0.0007942151133680373</t>
+          <t>6.05143721633894e-05 +/- 0.0010198063265569066</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0006354009077155886 +/- 0.0002854457226038335</t>
+          <t>-0.0006354009077155886 +/- 0.0004159675366071907</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.0005143721633887987 +/- 0.0007660507655777247</t>
+          <t>0.0016338880484115137 +/- 0.0007057127860629781</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.001694402420574903 +/- 0.0009961922924753093</t>
+          <t>0.002874432677760974 +/- 0.0014207996226170915</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0020574886535552396 +/- 0.0017051743181368242</t>
+          <t>-0.0022995461422087972 +/- 0.0012922333739221077</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0008169440242057569 +/- 0.001326148683861503</t>
+          <t>0.005113464447806304 +/- 0.000871175797209549</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0001210287443267788 +/- 0.00047263235557680667</t>
+          <t>-0.0007564296520423675 +/- 0.0003643447678908446</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.00042360060514372576 +/- 0.0005275520657840504</t>
+          <t>0.000605143721633894 +/- 0.0005579149444655357</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.000302571860816947 +/- 0.0006346800896642431</t>
+          <t>-0.0007866868381240621 +/- 0.00020070346688989</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.0006656580937972834 +/- 0.001553464163751112</t>
+          <t>0.006081694402420535 +/- 0.001692510289978457</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.0010287443267775864 +/- 0.0009961922924752661</t>
+          <t>-0.00042360060514372576 +/- 0.0011734172120826329</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.0004841149773071152 +/- 0.00038748104311243036</t>
+          <t>-0.0001512859304084735 +/- 0.00031004389609560356</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.001543116490166352 +/- 0.0013629174740762415</t>
+          <t>-3.02571860816947e-05 +/- 0.000695915279878978</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>0.0005446293494705045 +/- 0.0008955309281058327</t>
+          <t>-9.07715582450841e-05 +/- 0.001419510330498035</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0013313161875945668 +/- 0.0004528480952222666</t>
+          <t>0.0011195158850227037 +/- 0.0005249425589379014</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0011195158850226706 +/- 0.0008455787360049304</t>
+          <t>0.0005748865355521993 +/- 0.0005318727936837252</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.0039939485627836 +/- 0.0015055800671255285</t>
+          <t>-0.00042360060514372576 +/- 0.0009491308406268245</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.0028441754916793014 +/- 0.0010053402557238312</t>
+          <t>-0.002118003025718629 +/- 0.0005579149444655357</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.0007261724659606728 +/- 0.0012117993582148854</t>
+          <t>-0.001906202723146766 +/- 0.000766050765577748</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-0.0001512859304084735 +/- 0.00033828562443264927</t>
+          <t>-0.00021180030257186288 +/- 0.00019374052155621515</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.004750378214825957 +/- 0.0016519980265922941</t>
+          <t>-0.002904689863842691 +/- 0.000919738829262984</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-0.0026626323751890333 +/- 0.0009832421669755907</t>
+          <t>0.00045385779122542047 +/- 0.0007442283737518284</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.05143721633894e-05 +/- 0.0008319350732143815</t>
+          <t>-0.000695915279878978 +/- 0.0005421020534695641</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.009591527987897109 +/- 0.0015431164901664296</t>
+          <t>-0.004478063540090815 +/- 0.0014686427957048976</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-0.004236006051437147 +/- 0.0011321202380556667</t>
+          <t>0.0020574886535552396 +/- 0.0009355294906953377</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.008199697428139151 +/- 0.0015276133811031119</t>
+          <t>-0.003691376701966753 +/- 0.0016561491296101837</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.00039334341906203105 +/- 0.00027231467473525227</t>
+          <t>-0.0001512859304084735 +/- 0.00020297137465958957</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.000605143721633894 +/- 0.0006899700000599995</t>
+          <t>-0.002178517397882018 +/- 0.00044468800171555857</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.0021785173978819293 +/- 0.0006171279290278423</t>
+          <t>-0.0008774583963691463 +/- 0.0004774503430577808</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.000695915279878978 +/- 0.0004697178425494758</t>
+          <t>-0.00045385779122542047 +/- 0.0005284190377177958</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.0017851739788199317 +/- 0.001060729085806809</t>
+          <t>-0.0015431164901664296 +/- 0.0005143721633888099</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-0.0028441754916792017 +/- 0.0007913280986760526</t>
+          <t>-0.0005446293494705045 +/- 0.00032587986730012446</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.0009682299546142081 +/- 0.0013035194692004627</t>
+          <t>-0.0001815431164901682 +/- 0.0007185683562504105</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.0013918305597579229 +/- 0.000909730491883347</t>
+          <t>-0.001301059001512872 +/- 0.001419510330498035</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.00078668683812404 +/- 0.0007678413035067566</t>
+          <t>0.0001512859304084735 +/- 0.0004332169761959605</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0011195158850226482 +/- 0.0009668106086940831</t>
+          <t>0.000605143721633894 +/- 0.000605143721633894</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.007776096822995427 +/- 0.0006496493359632102</t>
+          <t>-0.0025718608169440493 +/- 0.0007063611213270116</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0008169440242057457 +/- 0.0006772474821663864</t>
+          <t>-0.0007866868381240621 +/- 0.00036308623298033634</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0004485741749439276 +/- 0.0010050872887765443</t>
+          <t>0.0021787888497276863 +/- 0.001303876318447671</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.003236142262095498 +/- 0.0012363845806840606</t>
+          <t>0.015636014098045527 +/- 0.0012719918770444788</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0004806151874399256 +/- 0.0008627306643919317</t>
+          <t>0.011118231336110274 +/- 0.00089543022188287</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.0029477731496315275 +/- 0.0015486121081184762</t>
+          <t>-0.0034924703620633933 +/- 0.0013089841855697278</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0005767382249279085 +/- 0.0014738865748157848</t>
+          <t>0.007818007049022779 +/- 0.0012752161962276394</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0021467478372316773 +/- 0.0013747797470634415</t>
+          <t>0.003876962512015414 +/- 0.002023663271341008</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0001281640499839809 +/- 0.0002563280999679618</t>
+          <t>0.00032041012495998 +/- 0.00024818861558524797</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0016981736622877276 +/- 0.0014404208133924432</t>
+          <t>-0.003909003524511334 +/- 0.0012959787514358675</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.0026914450496635543 +/- 0.00253589989585507</t>
+          <t>-0.022877282922140297 +/- 0.002511492206634454</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.007882089074014742 +/- 0.0033365757249458113</t>
+          <t>-0.015059275873117551 +/- 0.0036560466070095455</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0017622556872797235 +/- 0.001084198930835538</t>
+          <t>0.000448574174943972 +/- 0.0010352767972703252</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.001217558474847813 +/- 0.0010607462580741395</t>
+          <t>0.01614867029798146 +/- 0.0014626994182010006</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.0002563280999679729 +/- 0.0015749062130656275</t>
+          <t>0.010765780198654307 +/- 0.0013148532219598346</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.015347644985581554 +/- 0.002254057332516718</t>
+          <t>0.013264979173341917 +/- 0.0034574613163002206</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.012624158923422002 +/- 0.0011746429208473689</t>
+          <t>-0.004966356936879168 +/- 0.0014908542293023816</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0015059275873117728 +/- 0.0015100123893557562</t>
+          <t>0.0031720602371035356 +/- 0.0015791376520796834</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.002306952899711645 +/- 0.0012800374466798068</t>
+          <t>-0.005446972124319072 +/- 0.0008716097730685833</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.002146747837231655 +/- 0.0012162930404422988</t>
+          <t>-0.0008971483498878107 +/- 0.0015083117328984186</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.005446972124319149 +/- 0.0013518117981242755</t>
+          <t>0.0031079782121115505 +/- 0.0005176383986351686</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0003844921499519538 +/- 0.0001281640499839476</t>
+          <t>-0.0003844921499518983 +/- 0.0002793270710375125</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0069208586991348795 +/- 0.0018528461768408837</t>
+          <t>0.005543095161807165 +/- 0.0025514385199126573</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0025632809996796067 +/- 0.001857273533635318</t>
+          <t>0.0015059275873117838 +/- 0.0009180742570903168</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.0008651073373918572 +/- 0.0011733312030503503</t>
+          <t>-0.0034604293495674064 +/- 0.0010703808451451456</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0015379685998077707 +/- 0.0005695734967841032</t>
+          <t>-0.004101249599487333 +/- 0.0013038763184476704</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.002338993912207632 +/- 0.0012900238474333552</t>
+          <t>-0.0026273630246715363 +/- 0.001466904600097366</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0003524511374559225 +/- 0.0004632115442102151</t>
+          <t>0.0003524511374559891 +/- 0.0006319475464055222</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.003620634412047441 +/- 0.0017610901741315224</t>
+          <t>-0.001762255687279668 +/- 0.001991961684379294</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.0015059275873117617 +/- 0.0011992930004622161</t>
+          <t>-0.0021467478372316218 +/- 0.0015568767206993227</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.005382890099327131 +/- 0.0013502920541945073</t>
+          <t>0.002595322012175627 +/- 0.001332305215398381</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0007689842999038743 +/- 0.0009085195052071481</t>
+          <t>-0.0017942966997756549 +/- 0.0014414895071069437</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.001954501762255689 +/- 0.00041653316244792877</t>
+          <t>0.0008651073373919238 +/- 0.0006087792374239</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0006408202499198823 +/- 0.00047524501679562225</t>
+          <t>0.0013777635373278252 +/- 0.0002883691124639499</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.0019545017622556783 +/- 0.0014503646648838609</t>
+          <t>0.002723486062159608 +/- 0.0015181490215292737</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.002467157962191613 +/- 0.001137794354666102</t>
+          <t>-0.0010253123998717917 +/- 0.0012141810523227234</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.0002242870874719749 +/- 0.00020516258370499102</t>
+          <t>0.0001922460749760102 +/- 0.000434625439482571</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.0027555270746555836 +/- 0.0005942722521945333</t>
+          <t>0.0001281640499840253 +/- 0.000611303557460389</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0009932713873758493 +/- 0.0010076376285495982</t>
+          <t>-0.003973085549503319 +/- 0.0016966616206182297</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.0013777635373277807 +/- 0.001119603025290381</t>
+          <t>0.000352451137455978 +/- 0.0014644530447967211</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.0014738865748157638 +/- 0.0007049022749118893</t>
+          <t>0.0002883691124639931 +/- 0.0006636435494139168</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.0019545017622556783 +/- 0.001421769159393397</t>
+          <t>-0.004293495674463288 +/- 0.0014054285292830065</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.003652675424543406 +/- 0.0010742104847318067</t>
+          <t>0.0011214354373598634 +/- 0.0014203242716630332</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.00487023389939123 +/- 0.001319529656006016</t>
+          <t>0.004581864786927315 +/- 0.0010337882604871246</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.00746555591156679 +/- 0.0018575498930644898</t>
+          <t>-0.0037167574495353684 +/- 0.0022620137897754297</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.0012495994873437887 +/- 0.0018762468403661972</t>
+          <t>-0.0002563280999679063 +/- 0.0013426675321856459</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0038128804870234067 +/- 0.00101777508325977</t>
+          <t>-0.0015379685998077263 +/- 0.0014808356306685523</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0004806151874399256 +/- 0.0010746882301344567</t>
+          <t>0.0005767382249279529 +/- 0.0008452999652850249</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.0015700096123037466 +/- 0.00041653316244792785</t>
+          <t>0.0002883691124640042 +/- 0.00039111040101678354</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0009291893623838421 +/- 0.001037752947177291</t>
+          <t>0.000544697212431966 +/- 0.001482567805352029</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.005158603011855156 +/- 0.0010860910770059556</t>
+          <t>-0.007209227811598806 +/- 0.0021265675752701134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.009644344761294454 +/- 0.002360837810930942</t>
+          <t>-0.003684716437039348 +/- 0.0022712987630179003</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.0066965716116629045 +/- 0.0015262422766824065</t>
+          <t>0.0012816404998398424 +/- 0.002261105897388948</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3.20410124959869e-05 +/- 0.0006479893757179253</t>
+          <t>0.0004806151874399811 +/- 0.00038582488237080267</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0006087792374238731 +/- 0.0003345179913140118</t>
+          <t>-0.0019224607497596359 +/- 0.0006408202499198989</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0003524511374559447 +/- 0.0002242870874719432</t>
+          <t>0.0005767382249279529 +/- 0.0004001921178083116</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.0069208586991348795 +/- 0.001025312399871843</t>
+          <t>-0.0018904197372636377 +/- 0.0021081427939245068</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.0012495994873438 +/- 0.0017575889973601457</t>
+          <t>-0.0033963473245754217 +/- 0.0014836061394156083</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-0.0008651073373918461 +/- 0.0004763238944991475</t>
+          <t>-0.0022108298622235956 +/- 0.00041653316244792785</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.0017302146747837145 +/- 0.0007609318863850243</t>
+          <t>-0.0002242870874719194 +/- 0.0010337882604871224</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.0024671579621916018 +/- 0.0018849812342304265</t>
+          <t>0.0004806151874399589 +/- 0.001853123196529466</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.001089394424863832 +/- 0.0005586541420750697</t>
+          <t>-0.0007049022749118338 +/- 0.0006212982835522243</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.00016020506247999 +/- 0.0013230261340636065</t>
+          <t>-0.001762255687279668 +/- 0.0014908542293023757</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0029477731496315275 +/- 0.0015486121081185176</t>
+          <t>-0.0022108298622235956 +/- 0.0012280530532993985</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0018583787247677063 +/- 0.001759632197083732</t>
+          <t>0.009035565523870592 +/- 0.0025824340505748054</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0005446972124318993 +/- 0.0007984579169738559</t>
+          <t>-0.0014738865748157083 +/- 0.0005399647403509282</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-9.612303748798289e-05 +/- 0.00020516258370498409</t>
+          <t>-3.204101249596469e-05 +/- 0.0002661526389912771</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0025953220121755828 +/- 0.0006319475464054906</t>
+          <t>-0.000608779237423851 +/- 0.0016615049230969776</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.0014418455623197656 +/- 0.0015778368794931207</t>
+          <t>0.0008010253123999056 +/- 0.0012263799557196186</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.00038449214995193157 +/- 0.0007278318930855861</t>
+          <t>-0.0011534764498557504 +/- 0.00043462543948255306</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.0002563280999679618 +/- 0.0005873214604236902</t>
+          <t>0.000640820249919949 +/- 0.0010722973746031005</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.004069208586991358 +/- 0.0010436717382186738</t>
+          <t>0.0001281640499840253 +/- 0.001111781581089222</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-9.6123037487994e-05 +/- 0.0012577883003133871</t>
+          <t>-0.001762255687279668 +/- 0.0008745494433807268</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.000128164049983992 +/- 0.00015696826291466948</t>
+          <t>0.00032041012495998 +/- 0.0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.0009291893623838531 +/- 0.0005632296004885206</t>
+          <t>3.204101249604241e-05 +/- 0.0005055986490887419</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.0008971483498878441 +/- 0.0004709047887439873</t>
+          <t>-9.612303748792738e-05 +/- 0.0005371052423659198</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0006408202499198712 +/- 0.0004531283442400226</t>
+          <t>-0.0002563280999679063 +/- 0.0004250720654092112</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.001057353412367823 +/- 0.0008838906904283122</t>
+          <t>-0.0001281640499839254 +/- 0.0012752161962276281</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-6.4082024991996e-05 +/- 0.00019224607497598799</t>
+          <t>-0.00025632809996792847 +/- 0.0005126561999359194</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.003396347324575444 +/- 0.0009308451807967979</t>
+          <t>-0.00032041012495990227 +/- 0.0007164588200896528</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.0013777635373277807 +/- 0.0008838906904283026</t>
+          <t>0.002755527074655606 +/- 0.0006751460270972624</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>6.40820249919849e-05 +/- 0.000551254422751854</t>
+          <t>-6.40820249919627e-05 +/- 0.0005126561999359236</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.0016020506247997445 +/- 0.000797814777186088</t>
+          <t>0.0002242870874719971 +/- 0.0007313497091005015</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.004357577699455295 +/- 0.0014626994182010034</t>
+          <t>-0.0036526754245433833 +/- 0.0007473184101051061</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.00140980454982379 +/- 0.0010837253781024194</t>
+          <t>0.0019865427747517207 +/- 0.0006376080981138166</t>
         </is>
       </c>
     </row>
